--- a/data/export/2026-09-19-operations.xlsx
+++ b/data/export/2026-09-19-operations.xlsx
@@ -427,13 +427,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD21"/>
+  <dimension ref="A1:AD46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -648,27 +648,31 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:16</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr"/>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -676,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -700,33 +704,37 @@
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC2" s="2" t="inlineStr"/>
+      <c r="AC2" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -764,27 +772,31 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:19</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr"/>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -792,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -816,33 +828,37 @@
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB3" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC3" s="2" t="inlineStr"/>
+      <c r="AC3" s="2" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -880,27 +896,31 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:29</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -908,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -932,33 +952,37 @@
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC4" s="2" t="inlineStr"/>
+      <c r="AC4" s="2" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -996,27 +1020,31 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1024,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1048,33 +1076,37 @@
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC5" s="2" t="inlineStr"/>
+      <c r="AC5" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -1117,19 +1149,19 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:48</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：07:21采样，终点ETA 27分钟</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr"/>
@@ -1140,7 +1172,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1164,33 +1196,37 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1292,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1306,7 +1342,7 @@
       <c r="AC7" s="2" t="inlineStr"/>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
@@ -1349,19 +1385,19 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：07:21采样，终点ETA 48分钟</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr"/>
@@ -1372,7 +1408,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1401,7 +1437,7 @@
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
@@ -1422,7 +1458,7 @@
       <c r="AC8" s="2" t="inlineStr"/>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
@@ -1435,22 +1471,22 @@
       <c r="B9" s="2" t="inlineStr"/>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>沪A68397D</t>
+          <t>沪A31073D</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>07:05</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>07:15</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1488,7 +1524,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1502,7 +1538,7 @@
       <c r="U9" s="2" t="inlineStr"/>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:05</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
@@ -1538,35 +1574,35 @@
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>沪A15330A</t>
+          <t>沪A68397D</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1604,7 +1640,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1618,7 +1654,7 @@
       <c r="U10" s="2" t="inlineStr"/>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1654,35 +1690,35 @@
       <c r="AC10" s="2" t="inlineStr"/>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A35717D</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1715,12 +1751,12 @@
       <c r="N11" s="2" t="inlineStr"/>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1734,7 +1770,7 @@
       <c r="U11" s="2" t="inlineStr"/>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1770,35 +1806,35 @@
       <c r="AC11" s="2" t="inlineStr"/>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr"/>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>沪A68895D</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1836,7 +1872,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1850,7 +1886,7 @@
       <c r="U12" s="2" t="inlineStr"/>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -1875,46 +1911,50 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr"/>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A67353D</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1952,7 +1992,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1966,7 +2006,7 @@
       <c r="U13" s="2" t="inlineStr"/>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1991,46 +2031,50 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr"/>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2068,7 +2112,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2082,7 +2126,7 @@
       <c r="U14" s="2" t="inlineStr"/>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2107,46 +2151,50 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr"/>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2179,12 +2227,12 @@
       <c r="N15" s="2" t="inlineStr"/>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2198,7 +2246,7 @@
       <c r="U15" s="2" t="inlineStr"/>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
@@ -2234,35 +2282,35 @@
       <c r="AC15" s="2" t="inlineStr"/>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr"/>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2300,7 +2348,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2314,7 +2362,7 @@
       <c r="U16" s="2" t="inlineStr"/>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2339,46 +2387,50 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2411,12 +2463,12 @@
       <c r="N17" s="2" t="inlineStr"/>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2430,7 +2482,7 @@
       <c r="U17" s="2" t="inlineStr"/>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2455,18 +2507,22 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -2479,22 +2535,22 @@
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A15330A</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>06:05</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2527,12 +2583,12 @@
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2546,7 +2602,7 @@
       <c r="U18" s="2" t="inlineStr"/>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2582,35 +2638,35 @@
       <c r="AC18" s="2" t="inlineStr"/>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2625,30 +2681,30 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr"/>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：06:20采样，终点ETA 82分钟</t>
+          <t>尚无满足±5分钟标准的终点ETA</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2662,7 +2718,7 @@
       <c r="U19" s="2" t="inlineStr"/>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2677,7 +2733,7 @@
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>证据不足</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
@@ -2698,35 +2754,35 @@
       <c r="AC19" s="2" t="inlineStr"/>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>—/3</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>06:18</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2759,12 +2815,12 @@
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2778,7 +2834,7 @@
       <c r="U20" s="2" t="inlineStr"/>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>06:18</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2814,35 +2870,35 @@
       <c r="AC20" s="2" t="inlineStr"/>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>—/3</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2875,12 +2931,12 @@
       <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2894,7 +2950,7 @@
       <c r="U21" s="2" t="inlineStr"/>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -2930,7 +2986,2939 @@
       <c r="AC21" s="2" t="inlineStr"/>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>—/3</t>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr"/>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr"/>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr"/>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr"/>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC22" s="2" t="inlineStr"/>
+      <c r="AD22" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr"/>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr"/>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr"/>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr"/>
+      <c r="AD23" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr"/>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr"/>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr"/>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr"/>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr"/>
+      <c r="AD24" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr"/>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr"/>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr"/>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr"/>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr"/>
+      <c r="AD25" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr"/>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr"/>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr"/>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr"/>
+      <c r="AD26" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr"/>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr"/>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr"/>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr"/>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr"/>
+      <c r="AD27" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr"/>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr"/>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr"/>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr"/>
+      <c r="AD28" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr"/>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr"/>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr"/>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr"/>
+      <c r="AD29" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr"/>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr"/>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr"/>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr"/>
+      <c r="AD30" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr"/>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr"/>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr"/>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr"/>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr"/>
+      <c r="AD31" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr"/>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>沪A52272D</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr"/>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr"/>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr"/>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr"/>
+      <c r="AD32" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr"/>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr"/>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr"/>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr"/>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr"/>
+      <c r="AD33" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr"/>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr"/>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr"/>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr"/>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr"/>
+      <c r="AD34" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr"/>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr"/>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr"/>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr"/>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr"/>
+      <c r="AD35" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr"/>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>07:36</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>76分钟</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr"/>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr"/>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
+      <c r="AD36" s="2" t="inlineStr">
+        <is>
+          <t>1/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr"/>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>07:57</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>77分钟</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr"/>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr"/>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AD37" s="2" t="inlineStr">
+        <is>
+          <t>2/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr"/>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>86分钟</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr"/>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS末次终点ETA推算：07:20采样，终点ETA 51分钟</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr"/>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr"/>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr"/>
+      <c r="AD38" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr"/>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>沪A58633D</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>82分钟</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr"/>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr"/>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AD39" s="2" t="inlineStr">
+        <is>
+          <t>3/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr"/>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr"/>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr"/>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr"/>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr"/>
+      <c r="AD40" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr"/>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr"/>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr"/>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr"/>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr"/>
+      <c r="AD41" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr"/>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr"/>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr"/>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr"/>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr"/>
+      <c r="AD42" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr"/>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr"/>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr"/>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr"/>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
+      <c r="AD43" s="2" t="inlineStr">
+        <is>
+          <t>1/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr"/>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr"/>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr"/>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr"/>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr"/>
+      <c r="AD44" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr"/>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr"/>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr"/>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr"/>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr"/>
+      <c r="AD45" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr"/>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr"/>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr"/>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr"/>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AD46" s="2" t="inlineStr">
+        <is>
+          <t>2/9</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-19-operations.xlsx
+++ b/data/export/2026-09-19-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD46"/>
+  <dimension ref="A1:AD64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -452,7 +452,7 @@
     <col width="20" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
+    <col width="20" customWidth="1" min="23" max="23"/>
     <col width="12" customWidth="1" min="24" max="24"/>
     <col width="22" customWidth="1" min="25" max="25"/>
     <col width="14" customWidth="1" min="26" max="26"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -724,17 +724,17 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -1025,24 +1025,24 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AD5" s="2" t="inlineStr">
@@ -1144,27 +1144,31 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>07:48</t>
+          <t>07:46</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：07:21采样，终点ETA 27分钟</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1172,7 +1176,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1196,12 +1200,12 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
@@ -1221,12 +1225,12 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -1264,27 +1268,31 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:59</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr"/>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -1292,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1316,33 +1324,37 @@
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -1380,27 +1392,31 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>08:08</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：07:21采样，终点ETA 48分钟</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1408,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1432,33 +1448,37 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -1496,27 +1516,31 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1524,7 +1548,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1548,33 +1572,37 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC9" s="2" t="inlineStr"/>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -1612,27 +1640,31 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>66分钟</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1640,7 +1672,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1664,33 +1696,37 @@
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>66.0</t>
+        </is>
+      </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -1733,19 +1769,19 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr"/>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：08:11采样，终点ETA 23分钟</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr"/>
@@ -1756,7 +1792,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1780,33 +1816,37 @@
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -1849,19 +1889,19 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：08:11采样，终点ETA 27分钟</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr"/>
@@ -1872,7 +1912,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1896,17 +1936,17 @@
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1916,17 +1956,17 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -1992,7 +2032,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2046,7 +2086,7 @@
       </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -2112,7 +2152,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2151,7 +2191,7 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
@@ -2166,7 +2206,7 @@
       </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -2232,7 +2272,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2348,7 +2388,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2397,12 +2437,12 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2508,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2517,7 +2557,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AD17" s="2" t="inlineStr">
@@ -2529,28 +2569,28 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>沪A15330A</t>
+          <t>沪A66513D</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2583,12 +2623,12 @@
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2602,7 +2642,7 @@
       <c r="U18" s="2" t="inlineStr"/>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2627,46 +2667,50 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A31073D</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2704,7 +2748,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2718,7 +2762,7 @@
       <c r="U19" s="2" t="inlineStr"/>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2743,46 +2787,50 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>沪A68895D</t>
+          <t>沪A67983D</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2820,7 +2868,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2834,7 +2882,7 @@
       <c r="U20" s="2" t="inlineStr"/>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2859,46 +2907,50 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A35717D</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2931,12 +2983,12 @@
       <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2950,7 +3002,7 @@
       <c r="U21" s="2" t="inlineStr"/>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -2975,46 +3027,50 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr"/>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A68397D</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -3052,7 +3108,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3066,7 +3122,7 @@
       <c r="U22" s="2" t="inlineStr"/>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -3091,46 +3147,50 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>66.0</t>
+        </is>
+      </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr"/>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3163,12 +3223,12 @@
       <c r="N23" s="2" t="inlineStr"/>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3182,7 +3242,7 @@
       <c r="U23" s="2" t="inlineStr"/>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3207,18 +3267,22 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -3231,24 +3295,24 @@
       <c r="B24" s="2" t="inlineStr"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A15330A</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>06:05</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -3256,27 +3320,31 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr"/>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3284,7 +3352,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3298,7 +3366,7 @@
       <c r="U24" s="2" t="inlineStr"/>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3308,33 +3376,37 @@
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>2/24</t>
         </is>
       </c>
     </row>
@@ -3347,24 +3419,24 @@
       <c r="B25" s="2" t="inlineStr"/>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>07:00</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -3372,35 +3444,39 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr"/>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3414,7 +3490,7 @@
       <c r="U25" s="2" t="inlineStr"/>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3424,17 +3500,17 @@
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3444,13 +3520,17 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC25" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>4/24</t>
         </is>
       </c>
     </row>
@@ -3463,24 +3543,24 @@
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>06:18</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -3493,30 +3573,30 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：08:10采样，终点ETA 12分钟</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr"/>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3530,7 +3610,7 @@
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:18</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3540,17 +3620,17 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3560,13 +3640,17 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC26" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/24</t>
         </is>
       </c>
     </row>
@@ -3579,22 +3663,22 @@
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>沪A67057D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>07:12</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3627,12 +3711,12 @@
       <c r="N27" s="2" t="inlineStr"/>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3646,7 +3730,7 @@
       <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3682,7 +3766,7 @@
       <c r="AC27" s="2" t="inlineStr"/>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/24</t>
         </is>
       </c>
     </row>
@@ -3695,24 +3779,24 @@
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>07:15</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -3725,30 +3809,30 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：08:01采样，终点ETA 41分钟</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3762,7 +3846,7 @@
       <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3772,17 +3856,17 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3792,13 +3876,17 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC28" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>3/24</t>
         </is>
       </c>
     </row>
@@ -3811,22 +3899,22 @@
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3859,12 +3947,12 @@
       <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3878,7 +3966,7 @@
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:45</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3914,7 +4002,7 @@
       <c r="AC29" s="2" t="inlineStr"/>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/24</t>
         </is>
       </c>
     </row>
@@ -3927,22 +4015,22 @@
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3975,12 +4063,12 @@
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3994,7 +4082,7 @@
       <c r="U30" s="2" t="inlineStr"/>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4030,7 +4118,7 @@
       <c r="AC30" s="2" t="inlineStr"/>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/24</t>
         </is>
       </c>
     </row>
@@ -4043,22 +4131,22 @@
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -4091,12 +4179,12 @@
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4110,7 +4198,7 @@
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4146,7 +4234,7 @@
       <c r="AC31" s="2" t="inlineStr"/>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/24</t>
         </is>
       </c>
     </row>
@@ -4159,7 +4247,7 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A52272D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -4169,7 +4257,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -4207,12 +4295,12 @@
       <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4226,7 +4314,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4262,7 +4350,7 @@
       <c r="AC32" s="2" t="inlineStr"/>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/24</t>
         </is>
       </c>
     </row>
@@ -4275,22 +4363,22 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>07:45</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4323,12 +4411,12 @@
       <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4342,7 +4430,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4378,7 +4466,7 @@
       <c r="AC33" s="2" t="inlineStr"/>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/24</t>
         </is>
       </c>
     </row>
@@ -4391,22 +4479,22 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4439,12 +4527,12 @@
       <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4458,7 +4546,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4494,7 +4582,7 @@
       <c r="AC34" s="2" t="inlineStr"/>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/24</t>
         </is>
       </c>
     </row>
@@ -4507,22 +4595,22 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4555,12 +4643,12 @@
       <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4574,7 +4662,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4610,35 +4698,35 @@
       <c r="AC35" s="2" t="inlineStr"/>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/24</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4648,39 +4736,35 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>07:36</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr"/>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4694,7 +4778,7 @@
       <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4704,65 +4788,61 @@
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>证据不足</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC36" s="2" t="inlineStr">
-        <is>
-          <t>76.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr"/>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>1/9</t>
+          <t>—/24</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4772,39 +4852,35 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>07:57</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr"/>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr"/>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4818,7 +4894,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4828,65 +4904,61 @@
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>证据不足</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC37" s="2" t="inlineStr">
-        <is>
-          <t>77.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr"/>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>2/9</t>
+          <t>—/24</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A52272D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4901,30 +4973,30 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr"/>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：07:20采样，终点ETA 51分钟</t>
+          <t>尚无满足±5分钟标准的终点ETA</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4938,7 +5010,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -4953,7 +5025,7 @@
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>证据不足</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
@@ -4974,35 +5046,35 @@
       <c r="AC38" s="2" t="inlineStr"/>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/24</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A58633D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -5012,39 +5084,35 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr"/>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5058,7 +5126,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5068,17 +5136,17 @@
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>证据不足</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5088,45 +5156,41 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC39" s="2" t="inlineStr">
-        <is>
-          <t>82.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr"/>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>3/9</t>
+          <t>—/24</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -5159,12 +5223,12 @@
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5178,7 +5242,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5214,35 +5278,35 @@
       <c r="AC40" s="2" t="inlineStr"/>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/24</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -5275,12 +5339,12 @@
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5294,7 +5358,7 @@
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5330,35 +5394,35 @@
       <c r="AC41" s="2" t="inlineStr"/>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/24</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5391,12 +5455,12 @@
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5410,7 +5474,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5446,35 +5510,35 @@
       <c r="AC42" s="2" t="inlineStr"/>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/24</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5507,12 +5571,12 @@
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5526,7 +5590,7 @@
       <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5551,50 +5615,46 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC43" s="2" t="inlineStr">
-        <is>
-          <t>76.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr"/>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>1/9</t>
+          <t>—/24</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5627,12 +5687,12 @@
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5646,7 +5706,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5682,35 +5742,35 @@
       <c r="AC44" s="2" t="inlineStr"/>
       <c r="AD44" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/24</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5743,12 +5803,12 @@
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5762,7 +5822,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5798,35 +5858,35 @@
       <c r="AC45" s="2" t="inlineStr"/>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/24</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5859,12 +5919,12 @@
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5878,47 +5938,2191 @@
       <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr">
         <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr"/>
+      <c r="AD46" s="2" t="inlineStr">
+        <is>
+          <t>—/24</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr"/>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>沪A15330A</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr"/>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr"/>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr"/>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="AD47" s="2" t="inlineStr">
+        <is>
+          <t>2/24</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr"/>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr"/>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr"/>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr"/>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr"/>
+      <c r="AD48" s="2" t="inlineStr">
+        <is>
+          <t>—/24</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr"/>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>07:36</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>76分钟</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr"/>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr"/>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
+      <c r="AD49" s="2" t="inlineStr">
+        <is>
+          <t>1/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr"/>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>07:58</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>78分钟</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr"/>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr"/>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="AD50" s="2" t="inlineStr">
+        <is>
+          <t>2/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr"/>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>86分钟</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr"/>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr"/>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AD51" s="2" t="inlineStr">
+        <is>
+          <t>5/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr"/>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>沪A58633D</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>82分钟</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr"/>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr"/>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AD52" s="2" t="inlineStr">
+        <is>
+          <t>4/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr"/>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>101分钟</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr"/>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS末次终点ETA推算：08:00采样，终点ETA 50分钟</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr"/>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr"/>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr"/>
+      <c r="AD53" s="2" t="inlineStr">
+        <is>
+          <t>—/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr"/>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>08:41</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>81分钟</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr"/>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr"/>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AD54" s="2" t="inlineStr">
+        <is>
+          <t>3/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr"/>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr"/>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr"/>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr"/>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr"/>
+      <c r="AD55" s="2" t="inlineStr">
+        <is>
+          <t>—/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr"/>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr"/>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr"/>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr"/>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
+      <c r="AD56" s="2" t="inlineStr">
+        <is>
+          <t>1/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr"/>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr"/>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr"/>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr"/>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr"/>
+      <c r="AD57" s="2" t="inlineStr">
+        <is>
+          <t>—/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr"/>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr"/>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr"/>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr"/>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr"/>
+      <c r="AD58" s="2" t="inlineStr">
+        <is>
+          <t>—/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr"/>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
           <t>08:15</t>
         </is>
       </c>
-      <c r="W46" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr"/>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr"/>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr"/>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="X46" s="2" t="inlineStr">
+      <c r="X59" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="Y46" s="2" t="inlineStr">
+      <c r="Y59" s="2" t="inlineStr">
         <is>
           <t>证据不足</t>
         </is>
       </c>
-      <c r="Z46" s="2" t="inlineStr">
+      <c r="Z59" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA46" s="2" t="inlineStr">
+      <c r="AA59" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB46" s="2" t="inlineStr">
+      <c r="AB59" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AC46" s="2" t="inlineStr">
-        <is>
-          <t>77.0</t>
-        </is>
-      </c>
-      <c r="AD46" s="2" t="inlineStr">
-        <is>
-          <t>2/9</t>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AD59" s="2" t="inlineStr">
+        <is>
+          <t>5/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr"/>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr"/>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr"/>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr"/>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="AD60" s="2" t="inlineStr">
+        <is>
+          <t>2/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr"/>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr"/>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr"/>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr"/>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr"/>
+      <c r="AD61" s="2" t="inlineStr">
+        <is>
+          <t>—/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr"/>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>沪A58633D</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr"/>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr"/>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr"/>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AD62" s="2" t="inlineStr">
+        <is>
+          <t>4/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr"/>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr"/>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr"/>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr"/>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr"/>
+      <c r="AD63" s="2" t="inlineStr">
+        <is>
+          <t>—/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr"/>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr"/>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr"/>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr"/>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>终点确认到达+2分钟（覆盖计划时间）</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr"/>
+      <c r="AD64" s="2" t="inlineStr">
+        <is>
+          <t>—/11</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-19-operations.xlsx
+++ b/data/export/2026-09-19-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD64"/>
+  <dimension ref="A1:AD69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -452,7 +452,7 @@
     <col width="20" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="20" customWidth="1" min="23" max="23"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
     <col width="12" customWidth="1" min="24" max="24"/>
     <col width="22" customWidth="1" min="25" max="25"/>
     <col width="14" customWidth="1" min="26" max="26"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -843,22 +843,22 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB3" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -1645,24 +1645,24 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>66分钟</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="AD10" s="2" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1774,17 +1774,21 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr"/>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：08:11采样，终点ETA 23分钟</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -1792,7 +1796,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1816,12 +1820,12 @@
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
@@ -1841,7 +1845,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AD11" s="2" t="inlineStr">
@@ -1884,12 +1888,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1901,10 +1905,14 @@
       <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：08:11采样，终点ETA 27分钟</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1912,7 +1920,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1936,12 +1944,12 @@
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
@@ -1966,7 +1974,7 @@
       </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -2009,19 +2017,19 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr"/>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：08:21采样，终点ETA 28分钟</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr"/>
@@ -2032,7 +2040,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2056,37 +2064,37 @@
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -2152,7 +2160,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2272,7 +2280,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2388,7 +2396,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2442,7 +2450,7 @@
       </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2516,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2562,7 +2570,7 @@
       </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -2628,7 +2636,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2748,7 +2756,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2802,7 +2810,7 @@
       </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -2868,7 +2876,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2988,7 +2996,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3037,7 +3045,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AD21" s="2" t="inlineStr">
@@ -3108,7 +3116,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3157,7 +3165,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="AD22" s="2" t="inlineStr">
@@ -3175,22 +3183,22 @@
       <c r="B23" s="2" t="inlineStr"/>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>沪A68870D</t>
+          <t>沪A67353D</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>09:18</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3228,7 +3236,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3242,7 +3250,7 @@
       <c r="U23" s="2" t="inlineStr"/>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3272,45 +3280,45 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>沪A15330A</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3320,31 +3328,27 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr"/>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr"/>
       <c r="O24" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3352,7 +3356,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3366,7 +3370,7 @@
       <c r="U24" s="2" t="inlineStr"/>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3376,22 +3380,22 @@
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>证据不足</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
@@ -3401,12 +3405,12 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>2/24</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -3419,24 +3423,24 @@
       <c r="B25" s="2" t="inlineStr"/>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A15330A</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>06:05</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>06:10</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -3449,12 +3453,12 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr"/>
@@ -3476,7 +3480,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3490,7 +3494,7 @@
       <c r="U25" s="2" t="inlineStr"/>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3515,22 +3519,22 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>4/24</t>
+          <t>2/25</t>
         </is>
       </c>
     </row>
@@ -3543,24 +3547,24 @@
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>沪A68895D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>06:18</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -3568,7 +3572,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3578,17 +3582,21 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>125分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：08:10采样，终点ETA 12分钟</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3596,7 +3604,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3610,7 +3618,7 @@
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3620,12 +3628,12 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
@@ -3635,22 +3643,22 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>1/24</t>
+          <t>5/25</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3671,7 @@
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -3673,7 +3681,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:18</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -3688,27 +3696,31 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3716,7 +3728,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3730,7 +3742,7 @@
       <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:18</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3740,17 +3752,17 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3760,13 +3772,17 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC27" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>—/24</t>
+          <t>1/25</t>
         </is>
       </c>
     </row>
@@ -3779,24 +3795,24 @@
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>06:31</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -3809,19 +3825,19 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>131分钟</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：08:01采样，终点ETA 41分钟</t>
+          <t>SHMAAS末次终点ETA推算：08:20采样，终点ETA 20分钟</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr"/>
@@ -3832,7 +3848,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3856,7 +3872,7 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
@@ -3881,12 +3897,12 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>3/24</t>
+          <t>2/25</t>
         </is>
       </c>
     </row>
@@ -3899,24 +3915,24 @@
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>06:45</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -3924,35 +3940,39 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr"/>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3966,7 +3986,7 @@
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3976,17 +3996,17 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3996,13 +4016,17 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC29" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>—/24</t>
+          <t>2/25</t>
         </is>
       </c>
     </row>
@@ -4015,22 +4039,22 @@
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -4063,12 +4087,12 @@
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4082,7 +4106,7 @@
       <c r="U30" s="2" t="inlineStr"/>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:45</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4118,7 +4142,7 @@
       <c r="AC30" s="2" t="inlineStr"/>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>—/24</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -4131,24 +4155,24 @@
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>07:00</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -4161,30 +4185,30 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr"/>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：08:20采样，终点ETA 52分钟</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4198,7 +4222,7 @@
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4213,7 +4237,7 @@
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
@@ -4234,7 +4258,7 @@
       <c r="AC31" s="2" t="inlineStr"/>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>—/24</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -4247,22 +4271,22 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -4300,7 +4324,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4314,7 +4338,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4350,7 +4374,7 @@
       <c r="AC32" s="2" t="inlineStr"/>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>—/24</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4387,7 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A67057D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -4373,7 +4397,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -4411,12 +4435,12 @@
       <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4430,7 +4454,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4466,7 +4490,7 @@
       <c r="AC33" s="2" t="inlineStr"/>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>—/24</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -4479,22 +4503,22 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>07:15</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4532,7 +4556,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4546,7 +4570,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4582,7 +4606,7 @@
       <c r="AC34" s="2" t="inlineStr"/>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>—/24</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -4595,22 +4619,22 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4643,12 +4667,12 @@
       <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4662,7 +4686,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4698,7 +4722,7 @@
       <c r="AC35" s="2" t="inlineStr"/>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>—/24</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -4711,22 +4735,22 @@
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4759,12 +4783,12 @@
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4778,7 +4802,7 @@
       <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4814,7 +4838,7 @@
       <c r="AC36" s="2" t="inlineStr"/>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>—/24</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -4827,22 +4851,22 @@
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4880,7 +4904,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4930,7 +4954,7 @@
       <c r="AC37" s="2" t="inlineStr"/>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>—/24</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -4943,7 +4967,7 @@
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A52272D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -4953,7 +4977,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -4991,12 +5015,12 @@
       <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5010,7 +5034,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -5046,7 +5070,7 @@
       <c r="AC38" s="2" t="inlineStr"/>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>—/24</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -5059,22 +5083,22 @@
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A52272D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>07:45</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -5107,12 +5131,12 @@
       <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5126,7 +5150,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5162,7 +5186,7 @@
       <c r="AC39" s="2" t="inlineStr"/>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>—/24</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -5175,22 +5199,22 @@
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -5223,12 +5247,12 @@
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5242,7 +5266,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5278,7 +5302,7 @@
       <c r="AC40" s="2" t="inlineStr"/>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>—/24</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -5291,22 +5315,22 @@
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -5344,7 +5368,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5358,7 +5382,7 @@
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5394,7 +5418,7 @@
       <c r="AC41" s="2" t="inlineStr"/>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>—/24</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -5407,22 +5431,22 @@
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5455,12 +5479,12 @@
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5474,7 +5498,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5510,7 +5534,7 @@
       <c r="AC42" s="2" t="inlineStr"/>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>—/24</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -5523,22 +5547,22 @@
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>08:15</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5571,12 +5595,12 @@
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5590,7 +5614,7 @@
       <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5626,7 +5650,7 @@
       <c r="AC43" s="2" t="inlineStr"/>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>—/24</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -5639,22 +5663,22 @@
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>08:18</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5687,12 +5711,12 @@
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5706,7 +5730,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5742,7 +5766,7 @@
       <c r="AC44" s="2" t="inlineStr"/>
       <c r="AD44" s="2" t="inlineStr">
         <is>
-          <t>—/24</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -5755,7 +5779,7 @@
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -5765,7 +5789,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -5803,12 +5827,12 @@
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5822,7 +5846,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5858,7 +5882,7 @@
       <c r="AC45" s="2" t="inlineStr"/>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>—/24</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -5871,22 +5895,22 @@
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5924,7 +5948,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5938,7 +5962,7 @@
       <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -5974,7 +5998,7 @@
       <c r="AC46" s="2" t="inlineStr"/>
       <c r="AD46" s="2" t="inlineStr">
         <is>
-          <t>—/24</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -5987,22 +6011,22 @@
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A15330A</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>08:38</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -6040,7 +6064,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -6054,7 +6078,7 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -6079,22 +6103,18 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC47" s="2" t="inlineStr">
-        <is>
-          <t>130.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr"/>
       <c r="AD47" s="2" t="inlineStr">
         <is>
-          <t>2/24</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -6107,22 +6127,22 @@
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A15330A</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -6160,7 +6180,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6174,7 +6194,7 @@
       <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -6199,46 +6219,50 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB48" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC48" s="2" t="inlineStr"/>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AD48" s="2" t="inlineStr">
         <is>
-          <t>—/24</t>
+          <t>2/25</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -6248,39 +6272,35 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>07:36</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr"/>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N49" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6294,7 +6314,7 @@
       <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6304,65 +6324,61 @@
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>证据不足</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC49" s="2" t="inlineStr">
-        <is>
-          <t>76.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr"/>
       <c r="AD49" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -6372,39 +6388,35 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr"/>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N50" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6418,7 +6430,7 @@
       <c r="U50" s="2" t="inlineStr"/>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6428,65 +6440,61 @@
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>证据不足</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC50" s="2" t="inlineStr">
-        <is>
-          <t>78.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr"/>
       <c r="AD50" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6496,39 +6504,35 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr"/>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N51" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr"/>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6542,7 +6546,7 @@
       <c r="U51" s="2" t="inlineStr"/>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
@@ -6552,17 +6556,17 @@
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>证据不足</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
@@ -6577,12 +6581,12 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AD51" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>5/25</t>
         </is>
       </c>
     </row>
@@ -6595,24 +6599,24 @@
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>沪A58633D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>07:00</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -6625,34 +6629,34 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>07:36</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr"/>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6666,7 +6670,7 @@
       <c r="U52" s="2" t="inlineStr"/>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
@@ -6701,12 +6705,12 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AD52" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>1/12</t>
         </is>
       </c>
     </row>
@@ -6719,24 +6723,24 @@
       <c r="B53" s="2" t="inlineStr"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>07:10</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -6744,35 +6748,39 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>07:58</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>101分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr"/>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：08:00采样，终点ETA 50分钟</t>
-        </is>
-      </c>
-      <c r="N53" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6786,7 +6794,7 @@
       <c r="U53" s="2" t="inlineStr"/>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
@@ -6796,17 +6804,17 @@
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
@@ -6816,13 +6824,17 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC53" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
       <c r="AD53" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>2/12</t>
         </is>
       </c>
     </row>
@@ -6835,24 +6847,24 @@
       <c r="B54" s="2" t="inlineStr"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>07:20</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -6865,12 +6877,12 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr"/>
@@ -6892,7 +6904,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6906,7 +6918,7 @@
       <c r="U54" s="2" t="inlineStr"/>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:45</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
@@ -6931,22 +6943,22 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB54" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AD54" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>5/12</t>
         </is>
       </c>
     </row>
@@ -6959,24 +6971,24 @@
       <c r="B55" s="2" t="inlineStr"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A58633D</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>07:35</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -6984,27 +6996,31 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr"/>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N55" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -7012,7 +7028,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -7026,7 +7042,7 @@
       <c r="U55" s="2" t="inlineStr"/>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
@@ -7036,33 +7052,37 @@
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB55" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC55" s="2" t="inlineStr"/>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
       <c r="AD55" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>3/12</t>
         </is>
       </c>
     </row>
@@ -7075,24 +7095,24 @@
       <c r="B56" s="2" t="inlineStr"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A57022D</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>07:40</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -7105,19 +7125,19 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr"/>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：08:20采样，终点ETA 21分钟</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr"/>
@@ -7128,7 +7148,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -7142,7 +7162,7 @@
       <c r="U56" s="2" t="inlineStr"/>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
@@ -7152,17 +7172,17 @@
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
@@ -7177,12 +7197,12 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AD56" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>6/12</t>
         </is>
       </c>
     </row>
@@ -7195,24 +7215,24 @@
       <c r="B57" s="2" t="inlineStr"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>07:55</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -7220,35 +7240,39 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr"/>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N57" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -7262,7 +7286,7 @@
       <c r="U57" s="2" t="inlineStr"/>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
@@ -7272,33 +7296,37 @@
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB57" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC57" s="2" t="inlineStr"/>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
       <c r="AD57" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>4/12</t>
         </is>
       </c>
     </row>
@@ -7311,24 +7339,24 @@
       <c r="B58" s="2" t="inlineStr"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -7341,30 +7369,30 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>100分钟</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr"/>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：08:20采样，终点ETA 55分钟</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr"/>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7378,7 +7406,7 @@
       <c r="U58" s="2" t="inlineStr"/>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
@@ -7393,7 +7421,7 @@
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
@@ -7414,7 +7442,7 @@
       <c r="AC58" s="2" t="inlineStr"/>
       <c r="AD58" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -7427,7 +7455,7 @@
       <c r="B59" s="2" t="inlineStr"/>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -7437,7 +7465,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>07:40</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -7480,7 +7508,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7494,7 +7522,7 @@
       <c r="U59" s="2" t="inlineStr"/>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>07:40</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
@@ -7529,12 +7557,12 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AD59" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>1/12</t>
         </is>
       </c>
     </row>
@@ -7547,7 +7575,7 @@
       <c r="B60" s="2" t="inlineStr"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -7557,7 +7585,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -7595,12 +7623,12 @@
       <c r="N60" s="2" t="inlineStr"/>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7614,7 +7642,7 @@
       <c r="U60" s="2" t="inlineStr"/>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
@@ -7639,22 +7667,18 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC60" s="2" t="inlineStr">
-        <is>
-          <t>78.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr"/>
       <c r="AD60" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -7667,7 +7691,7 @@
       <c r="B61" s="2" t="inlineStr"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A51173D</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -7677,7 +7701,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -7715,12 +7739,12 @@
       <c r="N61" s="2" t="inlineStr"/>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7734,7 +7758,7 @@
       <c r="U61" s="2" t="inlineStr"/>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
@@ -7770,7 +7794,7 @@
       <c r="AC61" s="2" t="inlineStr"/>
       <c r="AD61" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -7783,22 +7807,22 @@
       <c r="B62" s="2" t="inlineStr"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>沪A58633D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -7831,12 +7855,12 @@
       <c r="N62" s="2" t="inlineStr"/>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7850,7 +7874,7 @@
       <c r="U62" s="2" t="inlineStr"/>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
@@ -7885,12 +7909,12 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AD62" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>5/12</t>
         </is>
       </c>
     </row>
@@ -7903,7 +7927,7 @@
       <c r="B63" s="2" t="inlineStr"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -7913,7 +7937,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -7951,12 +7975,12 @@
       <c r="N63" s="2" t="inlineStr"/>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -7970,7 +7994,7 @@
       <c r="U63" s="2" t="inlineStr"/>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
@@ -7995,18 +8019,22 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB63" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC63" s="2" t="inlineStr"/>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
       <c r="AD63" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>2/12</t>
         </is>
       </c>
     </row>
@@ -8019,7 +8047,7 @@
       <c r="B64" s="2" t="inlineStr"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -8029,7 +8057,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -8067,12 +8095,12 @@
       <c r="N64" s="2" t="inlineStr"/>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -8086,12 +8114,12 @@
       <c r="U64" s="2" t="inlineStr"/>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>终点确认到达+2分钟（覆盖计划时间）</t>
+          <t>计划发车</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
@@ -8111,7 +8139,7 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
@@ -8122,7 +8150,599 @@
       <c r="AC64" s="2" t="inlineStr"/>
       <c r="AD64" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr"/>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>沪A58633D</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr"/>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr"/>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr"/>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AD65" s="2" t="inlineStr">
+        <is>
+          <t>3/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr"/>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr"/>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr"/>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr"/>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr"/>
+      <c r="AD66" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr"/>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr"/>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr"/>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr"/>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AD67" s="2" t="inlineStr">
+        <is>
+          <t>6/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr"/>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr"/>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr"/>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr"/>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AD68" s="2" t="inlineStr">
+        <is>
+          <t>4/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr"/>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr"/>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr"/>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr"/>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr"/>
+      <c r="AD69" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-19-operations.xlsx
+++ b/data/export/2026-09-19-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD69"/>
+  <dimension ref="A1:AD93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -437,7 +437,7 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="36" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
@@ -447,12 +447,12 @@
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
     <col width="16" customWidth="1" min="19" max="19"/>
     <col width="20" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="36" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
+    <col width="20" customWidth="1" min="23" max="23"/>
     <col width="12" customWidth="1" min="24" max="24"/>
     <col width="22" customWidth="1" min="25" max="25"/>
     <col width="14" customWidth="1" min="26" max="26"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -853,7 +853,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AD3" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -972,17 +972,17 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1091,22 +1091,22 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1215,22 +1215,22 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1339,22 +1339,22 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1463,22 +1463,22 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1592,17 +1592,17 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -2012,7 +2012,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -2022,17 +2022,21 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr"/>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：08:21采样，终点ETA 28分钟</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -2040,7 +2044,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2064,12 +2068,12 @@
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
@@ -2089,7 +2093,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AD13" s="2" t="inlineStr">
@@ -2132,27 +2136,31 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>67分钟</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -2160,7 +2168,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2184,17 +2192,17 @@
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2204,17 +2212,17 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -2252,27 +2260,31 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr"/>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -2280,7 +2292,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2304,33 +2316,37 @@
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -2368,27 +2384,31 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -2396,7 +2416,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2420,37 +2440,37 @@
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -2488,27 +2508,31 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr"/>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -2516,7 +2540,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2540,37 +2564,37 @@
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB17" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -2608,27 +2632,31 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr"/>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -2636,7 +2664,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2660,37 +2688,37 @@
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB18" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -2733,19 +2761,19 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr"/>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：09:21采样，终点ETA 22分钟</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr"/>
@@ -2756,7 +2784,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2780,17 +2808,17 @@
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2800,17 +2828,17 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -2848,27 +2876,31 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr"/>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -2876,7 +2908,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2900,37 +2932,37 @@
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -2996,7 +3028,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3035,7 +3067,7 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
@@ -3116,7 +3148,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3155,7 +3187,7 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
@@ -3236,7 +3268,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3285,7 +3317,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AD23" s="2" t="inlineStr">
@@ -3303,22 +3335,22 @@
       <c r="B24" s="2" t="inlineStr"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>沪A68870D</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>09:18</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3351,12 +3383,12 @@
       <c r="N24" s="2" t="inlineStr"/>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3370,7 +3402,7 @@
       <c r="U24" s="2" t="inlineStr"/>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3395,7 +3427,7 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
@@ -3405,40 +3437,40 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr"/>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>沪A15330A</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3448,31 +3480,27 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr"/>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr"/>
       <c r="O25" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3480,7 +3508,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3494,7 +3522,7 @@
       <c r="U25" s="2" t="inlineStr"/>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3504,65 +3532,65 @@
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>证据不足</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>2/25</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3572,31 +3600,27 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr"/>
       <c r="O26" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3604,7 +3628,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3618,7 +3642,7 @@
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3628,65 +3652,65 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>证据不足</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>5/25</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>沪A68895D</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3696,31 +3720,27 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr"/>
       <c r="O27" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3728,7 +3748,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3742,7 +3762,7 @@
       <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3752,65 +3772,65 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>证据不足</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>1/25</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A67983D</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3825,19 +3845,19 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：08:20采样，终点ETA 20分钟</t>
+          <t>尚无满足±5分钟标准的终点ETA</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr"/>
@@ -3848,7 +3868,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3862,7 +3882,7 @@
       <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3872,65 +3892,65 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>证据不足</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>2/25</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A66513D</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3940,39 +3960,35 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr"/>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3986,7 +4002,7 @@
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3996,65 +4012,65 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>证据不足</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>2/25</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A68397D</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -4087,12 +4103,12 @@
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4106,7 +4122,7 @@
       <c r="U30" s="2" t="inlineStr"/>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4131,46 +4147,50 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC30" s="2" t="inlineStr"/>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A35717D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -4185,30 +4205,30 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>139分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr"/>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：08:20采样，终点ETA 52分钟</t>
+          <t>尚无满足±5分钟标准的终点ETA</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4222,7 +4242,7 @@
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4237,7 +4257,7 @@
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>证据不足</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
@@ -4247,18 +4267,22 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB31" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC31" s="2" t="inlineStr"/>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -4271,7 +4295,7 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A15330A</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -4281,7 +4305,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -4296,35 +4320,39 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr"/>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4338,7 +4366,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4348,33 +4376,37 @@
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC32" s="2" t="inlineStr"/>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>6/26</t>
         </is>
       </c>
     </row>
@@ -4387,7 +4419,7 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -4397,7 +4429,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -4412,35 +4444,39 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr"/>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4454,7 +4490,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4464,33 +4500,37 @@
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB33" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC33" s="2" t="inlineStr"/>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>8/26</t>
         </is>
       </c>
     </row>
@@ -4503,24 +4543,24 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A67057D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>06:18</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>07:12</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -4528,35 +4568,39 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr"/>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4570,7 +4614,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:18</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4580,33 +4624,37 @@
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC34" s="2" t="inlineStr"/>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>4/26</t>
         </is>
       </c>
     </row>
@@ -4619,7 +4667,7 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -4629,7 +4677,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -4644,35 +4692,39 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr"/>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4686,7 +4738,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4696,33 +4748,37 @@
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC35" s="2" t="inlineStr"/>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>8/26</t>
         </is>
       </c>
     </row>
@@ -4735,7 +4791,7 @@
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -4745,7 +4801,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -4760,35 +4816,39 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr"/>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4802,7 +4862,7 @@
       <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4812,33 +4872,37 @@
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB36" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC36" s="2" t="inlineStr"/>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>6/26</t>
         </is>
       </c>
     </row>
@@ -4851,7 +4915,7 @@
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -4861,7 +4925,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:45</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -4876,35 +4940,39 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr"/>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4918,7 +4986,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:45</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4928,33 +4996,37 @@
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC37" s="2" t="inlineStr"/>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>2/26</t>
         </is>
       </c>
     </row>
@@ -4967,7 +5039,7 @@
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -4977,7 +5049,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -4992,35 +5064,39 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr"/>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5034,7 +5110,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -5044,33 +5120,37 @@
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB38" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC38" s="2" t="inlineStr"/>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>11/26</t>
         </is>
       </c>
     </row>
@@ -5083,24 +5163,24 @@
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A52272D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -5108,35 +5188,39 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr"/>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5150,7 +5234,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5160,33 +5244,37 @@
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB39" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC39" s="2" t="inlineStr"/>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>1/26</t>
         </is>
       </c>
     </row>
@@ -5199,24 +5287,24 @@
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>07:45</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -5224,35 +5312,39 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr"/>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5266,7 +5358,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5276,33 +5368,37 @@
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB40" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC40" s="2" t="inlineStr"/>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>2/26</t>
         </is>
       </c>
     </row>
@@ -5315,7 +5411,7 @@
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -5325,7 +5421,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -5335,12 +5431,12 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程33%处后消失；随后反向物理轨迹由seq38推进至seq63，推进25站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
@@ -5363,12 +5459,12 @@
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5376,13 +5472,29 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R41" s="2" t="inlineStr"/>
-      <c r="S41" s="2" t="inlineStr"/>
-      <c r="T41" s="2" t="inlineStr"/>
-      <c r="U41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>物理seq22（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S41" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t>08:05</t>
+        </is>
+      </c>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq22映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±5分钟；反向位置物理seq38（站名待映射） ETA 9分钟参与校验</t>
+        </is>
+      </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5397,7 +5509,7 @@
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
@@ -5418,7 +5530,7 @@
       <c r="AC41" s="2" t="inlineStr"/>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -5431,7 +5543,7 @@
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -5441,7 +5553,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -5456,35 +5568,39 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr"/>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5498,7 +5614,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5508,17 +5624,17 @@
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5528,13 +5644,17 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC42" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>10/26</t>
         </is>
       </c>
     </row>
@@ -5547,7 +5667,7 @@
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -5557,7 +5677,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -5572,35 +5692,39 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr"/>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N43" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5614,7 +5738,7 @@
       <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5624,33 +5748,37 @@
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB43" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC43" s="2" t="inlineStr"/>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>4/26</t>
         </is>
       </c>
     </row>
@@ -5663,7 +5791,7 @@
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -5673,7 +5801,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -5711,12 +5839,12 @@
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5730,7 +5858,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5766,7 +5894,7 @@
       <c r="AC44" s="2" t="inlineStr"/>
       <c r="AD44" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -5779,7 +5907,7 @@
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -5789,7 +5917,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -5809,30 +5937,30 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr"/>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：09:20采样，终点ETA 25分钟</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5846,7 +5974,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5856,17 +5984,17 @@
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -5876,13 +6004,17 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC45" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>11/26</t>
         </is>
       </c>
     </row>
@@ -5895,7 +6027,7 @@
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A52272D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -5905,7 +6037,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -5943,12 +6075,12 @@
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5962,7 +6094,7 @@
       <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -5998,7 +6130,7 @@
       <c r="AC46" s="2" t="inlineStr"/>
       <c r="AD46" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -6011,7 +6143,7 @@
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -6021,7 +6153,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -6059,12 +6191,12 @@
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -6078,7 +6210,7 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -6114,7 +6246,7 @@
       <c r="AC47" s="2" t="inlineStr"/>
       <c r="AD47" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -6127,7 +6259,7 @@
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A15330A</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -6137,7 +6269,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -6175,12 +6307,12 @@
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6194,7 +6326,7 @@
       <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -6219,22 +6351,18 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC48" s="2" t="inlineStr">
-        <is>
-          <t>130.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr"/>
       <c r="AD48" s="2" t="inlineStr">
         <is>
-          <t>2/25</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -6247,7 +6375,7 @@
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -6257,7 +6385,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -6295,12 +6423,12 @@
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6314,7 +6442,7 @@
       <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6350,7 +6478,7 @@
       <c r="AC49" s="2" t="inlineStr"/>
       <c r="AD49" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -6363,7 +6491,7 @@
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -6373,7 +6501,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -6411,12 +6539,12 @@
       <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6430,7 +6558,7 @@
       <c r="U50" s="2" t="inlineStr"/>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6466,7 +6594,7 @@
       <c r="AC50" s="2" t="inlineStr"/>
       <c r="AD50" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -6479,7 +6607,7 @@
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -6489,7 +6617,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -6527,12 +6655,12 @@
       <c r="N51" s="2" t="inlineStr"/>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6546,7 +6674,7 @@
       <c r="U51" s="2" t="inlineStr"/>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
@@ -6571,50 +6699,46 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC51" s="2" t="inlineStr">
-        <is>
-          <t>132.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr"/>
       <c r="AD51" s="2" t="inlineStr">
         <is>
-          <t>5/25</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6624,39 +6748,35 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>07:36</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr"/>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N52" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr"/>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6670,7 +6790,7 @@
       <c r="U52" s="2" t="inlineStr"/>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
@@ -6680,65 +6800,61 @@
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>证据不足</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC52" s="2" t="inlineStr">
-        <is>
-          <t>76.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr"/>
       <c r="AD52" s="2" t="inlineStr">
         <is>
-          <t>1/12</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6748,39 +6864,35 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr"/>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N53" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr"/>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6794,7 +6906,7 @@
       <c r="U53" s="2" t="inlineStr"/>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
@@ -6804,65 +6916,61 @@
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>证据不足</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC53" s="2" t="inlineStr">
-        <is>
-          <t>78.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr"/>
       <c r="AD53" s="2" t="inlineStr">
         <is>
-          <t>2/12</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6872,39 +6980,35 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr"/>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N54" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr"/>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6918,7 +7022,7 @@
       <c r="U54" s="2" t="inlineStr"/>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
@@ -6928,65 +7032,61 @@
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>证据不足</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC54" s="2" t="inlineStr">
-        <is>
-          <t>86.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr"/>
       <c r="AD54" s="2" t="inlineStr">
         <is>
-          <t>5/12</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>沪A58633D</t>
+          <t>沪A15330A</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6996,39 +7096,35 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr"/>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
-        </is>
-      </c>
-      <c r="N55" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr"/>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -7042,7 +7138,7 @@
       <c r="U55" s="2" t="inlineStr"/>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
@@ -7052,17 +7148,17 @@
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>证据不足</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
@@ -7077,40 +7173,40 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AD55" s="2" t="inlineStr">
         <is>
-          <t>3/12</t>
+          <t>6/26</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -7125,30 +7221,30 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>91分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr"/>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：08:20采样，终点ETA 21分钟</t>
+          <t>尚无满足±5分钟标准的终点ETA</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr"/>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -7162,7 +7258,7 @@
       <c r="U56" s="2" t="inlineStr"/>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
@@ -7172,65 +7268,61 @@
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>证据不足</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC56" s="2" t="inlineStr">
-        <is>
-          <t>91.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr"/>
       <c r="AD56" s="2" t="inlineStr">
         <is>
-          <t>6/12</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -7240,39 +7332,35 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr"/>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N57" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr"/>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -7286,7 +7374,7 @@
       <c r="U57" s="2" t="inlineStr"/>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
@@ -7296,65 +7384,61 @@
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>证据不足</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC57" s="2" t="inlineStr">
-        <is>
-          <t>82.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr"/>
       <c r="AD57" s="2" t="inlineStr">
         <is>
-          <t>4/12</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -7369,30 +7453,30 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>100分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr"/>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：08:20采样，终点ETA 55分钟</t>
+          <t>尚无满足±5分钟标准的终点ETA</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr"/>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7406,7 +7490,7 @@
       <c r="U58" s="2" t="inlineStr"/>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
@@ -7421,7 +7505,7 @@
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>证据不足</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
@@ -7431,46 +7515,50 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB58" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC58" s="2" t="inlineStr"/>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AD58" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>4/26</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr"/>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -7503,12 +7591,12 @@
       <c r="N59" s="2" t="inlineStr"/>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7522,7 +7610,7 @@
       <c r="U59" s="2" t="inlineStr"/>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
@@ -7557,40 +7645,40 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AD59" s="2" t="inlineStr">
         <is>
-          <t>1/12</t>
+          <t>8/26</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -7623,12 +7711,12 @@
       <c r="N60" s="2" t="inlineStr"/>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7642,7 +7730,7 @@
       <c r="U60" s="2" t="inlineStr"/>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
@@ -7667,46 +7755,50 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB60" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC60" s="2" t="inlineStr"/>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
       <c r="AD60" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>8/26</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -7739,12 +7831,12 @@
       <c r="N61" s="2" t="inlineStr"/>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7758,7 +7850,7 @@
       <c r="U61" s="2" t="inlineStr"/>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
@@ -7783,46 +7875,50 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB61" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC61" s="2" t="inlineStr"/>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AD61" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>6/26</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -7855,12 +7951,12 @@
       <c r="N62" s="2" t="inlineStr"/>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7874,7 +7970,7 @@
       <c r="U62" s="2" t="inlineStr"/>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
@@ -7909,40 +8005,40 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AD62" s="2" t="inlineStr">
         <is>
-          <t>5/12</t>
+          <t>2/26</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -7975,12 +8071,12 @@
       <c r="N63" s="2" t="inlineStr"/>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -7994,7 +8090,7 @@
       <c r="U63" s="2" t="inlineStr"/>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
@@ -8029,40 +8125,40 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AD63" s="2" t="inlineStr">
         <is>
-          <t>2/12</t>
+          <t>11/26</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A79307D</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -8095,12 +8191,12 @@
       <c r="N64" s="2" t="inlineStr"/>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -8114,7 +8210,7 @@
       <c r="U64" s="2" t="inlineStr"/>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
@@ -8150,35 +8246,35 @@
       <c r="AC64" s="2" t="inlineStr"/>
       <c r="AD64" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>沪A58633D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -8211,12 +8307,12 @@
       <c r="N65" s="2" t="inlineStr"/>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8230,7 +8326,7 @@
       <c r="U65" s="2" t="inlineStr"/>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
@@ -8265,40 +8361,40 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AD65" s="2" t="inlineStr">
         <is>
-          <t>3/12</t>
+          <t>1/26</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -8331,12 +8427,12 @@
       <c r="N66" s="2" t="inlineStr"/>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8350,7 +8446,7 @@
       <c r="U66" s="2" t="inlineStr"/>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
@@ -8375,46 +8471,50 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB66" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC66" s="2" t="inlineStr"/>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
       <c r="AD66" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>2/26</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr"/>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -8447,12 +8547,12 @@
       <c r="N67" s="2" t="inlineStr"/>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8466,7 +8566,7 @@
       <c r="U67" s="2" t="inlineStr"/>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
@@ -8501,12 +8601,12 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AD67" s="2" t="inlineStr">
         <is>
-          <t>6/12</t>
+          <t>4/26</t>
         </is>
       </c>
     </row>
@@ -8519,7 +8619,7 @@
       <c r="B68" s="2" t="inlineStr"/>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -8529,7 +8629,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -8544,27 +8644,31 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:36</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr"/>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N68" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -8572,7 +8676,7 @@
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8586,7 +8690,7 @@
       <c r="U68" s="2" t="inlineStr"/>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
@@ -8596,37 +8700,37 @@
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB68" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AD68" s="2" t="inlineStr">
         <is>
-          <t>4/12</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -8639,7 +8743,7 @@
       <c r="B69" s="2" t="inlineStr"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -8649,7 +8753,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -8664,35 +8768,39 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:58</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr"/>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N69" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8706,43 +8814,2943 @@
       <c r="U69" s="2" t="inlineStr"/>
       <c r="V69" s="2" t="inlineStr">
         <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AD69" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr"/>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>86分钟</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr"/>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr"/>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>84.5</t>
+        </is>
+      </c>
+      <c r="AD70" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr"/>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>沪A58633D</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>81分钟</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr"/>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr"/>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AD71" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr"/>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>08:34</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>84分钟</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr"/>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr"/>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AD72" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr"/>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>08:42</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>82分钟</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr"/>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr"/>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AD73" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr"/>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>80分钟</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr"/>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr"/>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AD74" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr"/>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>81分钟</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr"/>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr"/>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>78.5</t>
+        </is>
+      </c>
+      <c r="AD75" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr"/>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>85分钟</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr"/>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr"/>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AD76" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr"/>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>81分钟</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr"/>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr"/>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AD77" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr"/>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>83分钟</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr"/>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr"/>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>84.5</t>
+        </is>
+      </c>
+      <c r="AD78" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr"/>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>09:43</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>88分钟</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr"/>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS末次终点ETA推算：09:20采样，终点ETA 23分钟</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr"/>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr"/>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>末次终点ETA兜底</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AD79" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr"/>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr"/>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr"/>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr"/>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr"/>
+      <c r="AD80" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr"/>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>沪A58633D</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>105分钟</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr"/>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS末次终点ETA推算：09:20采样，终点ETA 55分钟</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr"/>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr"/>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AD81" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr"/>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr"/>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr"/>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr"/>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr"/>
+      <c r="AD82" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr"/>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr"/>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr"/>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr"/>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AD83" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr"/>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="W69" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr"/>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr"/>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr"/>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="X69" s="2" t="inlineStr">
+      <c r="X84" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="Y69" s="2" t="inlineStr">
+      <c r="Y84" s="2" t="inlineStr">
         <is>
           <t>证据不足</t>
         </is>
       </c>
-      <c r="Z69" s="2" t="inlineStr">
+      <c r="Z84" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA69" s="2" t="inlineStr">
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB69" s="2" t="inlineStr">
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AD84" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr"/>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr"/>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr"/>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr"/>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AC69" s="2" t="inlineStr"/>
-      <c r="AD69" s="2" t="inlineStr">
-        <is>
-          <t>—/12</t>
+      <c r="AC85" s="2" t="inlineStr"/>
+      <c r="AD85" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr"/>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr"/>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr"/>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr"/>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr"/>
+      <c r="AD86" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr"/>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr"/>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr"/>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr"/>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr"/>
+      <c r="AD87" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr"/>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr"/>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr"/>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr"/>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AD88" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr"/>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr"/>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr"/>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr"/>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AD89" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr"/>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr"/>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr"/>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr"/>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>78.5</t>
+        </is>
+      </c>
+      <c r="AD90" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr"/>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr"/>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr"/>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr"/>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>终点确认到达+2分钟（覆盖计划时间）</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AD91" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr"/>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr"/>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr"/>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr"/>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AD92" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr"/>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr"/>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr"/>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr"/>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>84.5</t>
+        </is>
+      </c>
+      <c r="AD93" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-19-operations.xlsx
+++ b/data/export/2026-09-19-operations.xlsx
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -724,12 +724,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AD8" s="2" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1964,12 +1964,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AD12" s="2" t="inlineStr">
@@ -2098,7 +2098,7 @@
       </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -2292,7 +2292,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -2664,7 +2664,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -2912,7 +2912,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2956,12 +2956,12 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AD20" s="2" t="inlineStr">
@@ -3036,7 +3036,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3085,12 +3085,12 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -3338,7 +3338,7 @@
       </c>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -3408,7 +3408,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3457,12 +3457,12 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -3904,7 +3904,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AD28" s="2" t="inlineStr">
@@ -4028,7 +4028,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4573,12 +4573,12 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -4896,7 +4896,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5193,12 +5193,12 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -5392,7 +5392,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -5694,7 +5694,7 @@
       </c>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -5764,7 +5764,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AD43" s="2" t="inlineStr">
@@ -5942,7 +5942,7 @@
       </c>
       <c r="AD44" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -6260,7 +6260,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -6562,7 +6562,7 @@
       </c>
       <c r="AD49" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -6632,7 +6632,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6676,12 +6676,12 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AD50" s="2" t="inlineStr">
@@ -6756,7 +6756,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6805,12 +6805,12 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AD51" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -7058,7 +7058,7 @@
       </c>
       <c r="AD53" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -7252,7 +7252,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -7301,12 +7301,12 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AD55" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -7550,7 +7550,7 @@
       </c>
       <c r="AD57" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -7616,7 +7616,7 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7660,12 +7660,12 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AD58" s="2" t="inlineStr">
@@ -7740,7 +7740,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7784,12 +7784,12 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AD59" s="2" t="inlineStr">
@@ -7864,7 +7864,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7913,12 +7913,12 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AD60" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="AD61" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -8236,7 +8236,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -8285,12 +8285,12 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AD63" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -8732,7 +8732,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8776,12 +8776,12 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AD67" s="2" t="inlineStr">
@@ -8856,7 +8856,7 @@
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8900,12 +8900,12 @@
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AD68" s="2" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -9228,7 +9228,7 @@
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AD71" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -9476,7 +9476,7 @@
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -9525,12 +9525,12 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AD73" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -9697,24 +9697,24 @@
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr"/>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
@@ -9724,7 +9724,7 @@
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -9768,12 +9768,12 @@
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AD75" s="2" t="inlineStr">
@@ -9848,7 +9848,7 @@
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -9940,27 +9940,31 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>21:07</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr"/>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：20:21采样，终点ETA 46分钟</t>
-        </is>
-      </c>
-      <c r="N77" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9968,7 +9972,7 @@
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -9992,17 +9996,17 @@
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
@@ -10012,12 +10016,12 @@
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AD77" s="2" t="inlineStr">
@@ -10060,29 +10064,29 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr"/>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>20:21采样：该车到重点站唐陆公路川桥路 ETA 16分钟；叠加该车自身同类时段从该站到终点历史中位数43分钟，约±6分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O78" s="2" t="inlineStr">
@@ -10092,7 +10096,7 @@
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -10116,12 +10120,12 @@
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
@@ -10141,12 +10145,12 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AD78" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -10184,29 +10188,29 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>21:51</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr"/>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数81分钟估算，约±8分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
@@ -10216,7 +10220,7 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -10240,12 +10244,12 @@
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr">
@@ -10265,12 +10269,12 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AD79" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -10313,7 +10317,7 @@
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>22:13</t>
+          <t>22:12</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
@@ -10325,14 +10329,10 @@
       <c r="L80" s="2" t="inlineStr"/>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数78分钟估算，约±8分钟</t>
-        </is>
-      </c>
-      <c r="N80" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：21:21采样，终点ETA 51分钟</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr"/>
       <c r="O80" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10340,7 +10340,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -10364,17 +10364,17 @@
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA80" s="2" t="inlineStr">
@@ -10384,12 +10384,12 @@
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AD80" s="2" t="inlineStr">
@@ -10437,19 +10437,19 @@
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>22:27</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr"/>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±5分钟</t>
+          <t>21:21采样：该车到重点站唐陆公路春雅路 ETA 31分钟；叠加该车自身同类时段从该站到终点历史中位数38分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -10464,7 +10464,7 @@
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -10493,7 +10493,7 @@
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr">
@@ -10508,12 +10508,12 @@
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AD81" s="2" t="inlineStr">
@@ -10642,7 +10642,7 @@
       </c>
       <c r="AD82" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="AD83" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -10836,7 +10836,7 @@
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>130.8</t>
+          <t>132.2</t>
         </is>
       </c>
       <c r="AD84" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -11014,7 +11014,7 @@
       </c>
       <c r="AD85" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -11138,7 +11138,7 @@
       </c>
       <c r="AD86" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -11208,7 +11208,7 @@
       </c>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q87" s="2" t="inlineStr">
@@ -11257,7 +11257,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>130.2</t>
+          <t>128.8</t>
         </is>
       </c>
       <c r="AD87" s="2" t="inlineStr">
@@ -11386,7 +11386,7 @@
       </c>
       <c r="AD88" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -11580,7 +11580,7 @@
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -11629,12 +11629,12 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>135.2</t>
+          <t>134.8</t>
         </is>
       </c>
       <c r="AD90" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -11840,7 +11840,7 @@
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -11889,12 +11889,12 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AD92" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -11964,7 +11964,7 @@
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -12018,7 +12018,7 @@
       </c>
       <c r="AD93" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -12088,7 +12088,7 @@
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
@@ -12132,17 +12132,17 @@
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>136.2</t>
         </is>
       </c>
       <c r="AD94" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -12212,7 +12212,7 @@
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -12261,12 +12261,12 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AD95" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -12390,7 +12390,7 @@
       </c>
       <c r="AD96" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -12514,7 +12514,7 @@
       </c>
       <c r="AD97" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -12584,7 +12584,7 @@
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr">
@@ -12633,12 +12633,12 @@
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>140.8</t>
+          <t>138.2</t>
         </is>
       </c>
       <c r="AD98" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -12708,7 +12708,7 @@
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q99" s="2" t="inlineStr">
@@ -12752,17 +12752,17 @@
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>135.3</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="AD99" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -12832,7 +12832,7 @@
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q100" s="2" t="inlineStr">
@@ -12881,12 +12881,12 @@
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>146.7</t>
+          <t>145.3</t>
         </is>
       </c>
       <c r="AD100" s="2" t="inlineStr">
         <is>
-          <t>27/29</t>
+          <t>28/29</t>
         </is>
       </c>
     </row>
@@ -13080,7 +13080,7 @@
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q102" s="2" t="inlineStr">
@@ -13124,17 +13124,17 @@
       </c>
       <c r="AB102" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>134.8</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AD102" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -13204,7 +13204,7 @@
       </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q103" s="2" t="inlineStr">
@@ -13248,17 +13248,17 @@
       </c>
       <c r="AB103" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AD103" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -13506,7 +13506,7 @@
       </c>
       <c r="AD105" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -13630,7 +13630,7 @@
       </c>
       <c r="AD106" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -13696,7 +13696,7 @@
       </c>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q107" s="2" t="inlineStr">
@@ -13740,17 +13740,17 @@
       </c>
       <c r="AB107" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC107" s="2" t="inlineStr">
         <is>
-          <t>133.8</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AD107" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -13820,7 +13820,7 @@
       </c>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q108" s="2" t="inlineStr">
@@ -13869,12 +13869,12 @@
       </c>
       <c r="AC108" s="2" t="inlineStr">
         <is>
-          <t>130.8</t>
+          <t>132.2</t>
         </is>
       </c>
       <c r="AD108" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -13998,7 +13998,7 @@
       </c>
       <c r="AD109" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -14122,7 +14122,7 @@
       </c>
       <c r="AD110" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -14246,7 +14246,7 @@
       </c>
       <c r="AD111" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -14316,7 +14316,7 @@
       </c>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q112" s="2" t="inlineStr">
@@ -14365,7 +14365,7 @@
       </c>
       <c r="AC112" s="2" t="inlineStr">
         <is>
-          <t>130.2</t>
+          <t>128.8</t>
         </is>
       </c>
       <c r="AD112" s="2" t="inlineStr">
@@ -14494,7 +14494,7 @@
       </c>
       <c r="AD113" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -14820,7 +14820,7 @@
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q116" s="2" t="inlineStr">
@@ -14869,12 +14869,12 @@
       </c>
       <c r="AC116" s="2" t="inlineStr">
         <is>
-          <t>135.2</t>
+          <t>134.8</t>
         </is>
       </c>
       <c r="AD116" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -14944,7 +14944,7 @@
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q117" s="2" t="inlineStr">
@@ -14993,12 +14993,12 @@
       </c>
       <c r="AC117" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AD117" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -15068,7 +15068,7 @@
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q118" s="2" t="inlineStr">
@@ -15122,7 +15122,7 @@
       </c>
       <c r="AD118" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -15192,7 +15192,7 @@
       </c>
       <c r="P119" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q119" s="2" t="inlineStr">
@@ -15236,17 +15236,17 @@
       </c>
       <c r="AB119" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC119" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>136.2</t>
         </is>
       </c>
       <c r="AD119" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -15370,7 +15370,7 @@
       </c>
       <c r="AD120" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -15494,7 +15494,7 @@
       </c>
       <c r="AD121" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -15564,7 +15564,7 @@
       </c>
       <c r="P122" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q122" s="2" t="inlineStr">
@@ -15613,12 +15613,12 @@
       </c>
       <c r="AC122" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AD122" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -15688,7 +15688,7 @@
       </c>
       <c r="P123" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q123" s="2" t="inlineStr">
@@ -15732,17 +15732,17 @@
       </c>
       <c r="AB123" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC123" s="2" t="inlineStr">
         <is>
-          <t>135.3</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="AD123" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -15936,7 +15936,7 @@
       </c>
       <c r="P125" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q125" s="2" t="inlineStr">
@@ -15985,12 +15985,12 @@
       </c>
       <c r="AC125" s="2" t="inlineStr">
         <is>
-          <t>140.8</t>
+          <t>138.2</t>
         </is>
       </c>
       <c r="AD125" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -16184,7 +16184,7 @@
       </c>
       <c r="P127" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q127" s="2" t="inlineStr">
@@ -16228,17 +16228,17 @@
       </c>
       <c r="AB127" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC127" s="2" t="inlineStr">
         <is>
-          <t>134.8</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AD127" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -16358,7 +16358,7 @@
       </c>
       <c r="AD128" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -16428,7 +16428,7 @@
       </c>
       <c r="P129" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q129" s="2" t="inlineStr">
@@ -16472,17 +16472,17 @@
       </c>
       <c r="AB129" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC129" s="2" t="inlineStr">
         <is>
-          <t>133.8</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AD129" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -16606,7 +16606,7 @@
       </c>
       <c r="AD130" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -16858,7 +16858,7 @@
       </c>
       <c r="AD132" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -17176,7 +17176,7 @@
       </c>
       <c r="P135" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q135" s="2" t="inlineStr">
@@ -17225,12 +17225,12 @@
       </c>
       <c r="AC135" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>131.3</t>
         </is>
       </c>
       <c r="AD135" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -17354,7 +17354,7 @@
       </c>
       <c r="AD136" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -17478,7 +17478,7 @@
       </c>
       <c r="AD137" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -17672,7 +17672,7 @@
       </c>
       <c r="P139" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q139" s="2" t="inlineStr">
@@ -17721,12 +17721,12 @@
       </c>
       <c r="AC139" s="2" t="inlineStr">
         <is>
-          <t>140.8</t>
+          <t>138.2</t>
         </is>
       </c>
       <c r="AD139" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -17974,7 +17974,7 @@
       </c>
       <c r="AD141" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AD142" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -18218,7 +18218,7 @@
       </c>
       <c r="AD143" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -18342,7 +18342,7 @@
       </c>
       <c r="AD144" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -18466,7 +18466,7 @@
       </c>
       <c r="AD145" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -18788,7 +18788,7 @@
       </c>
       <c r="P148" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q148" s="2" t="inlineStr">
@@ -18837,12 +18837,12 @@
       </c>
       <c r="AC148" s="2" t="inlineStr">
         <is>
-          <t>135.2</t>
+          <t>134.8</t>
         </is>
       </c>
       <c r="AD148" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -18912,7 +18912,7 @@
       </c>
       <c r="P149" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q149" s="2" t="inlineStr">
@@ -18961,12 +18961,12 @@
       </c>
       <c r="AC149" s="2" t="inlineStr">
         <is>
-          <t>146.7</t>
+          <t>145.3</t>
         </is>
       </c>
       <c r="AD149" s="2" t="inlineStr">
         <is>
-          <t>27/29</t>
+          <t>28/29</t>
         </is>
       </c>
     </row>
@@ -19036,7 +19036,7 @@
       </c>
       <c r="P150" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q150" s="2" t="inlineStr">
@@ -19080,17 +19080,17 @@
       </c>
       <c r="AB150" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC150" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AD150" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -19160,7 +19160,7 @@
       </c>
       <c r="P151" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q151" s="2" t="inlineStr">
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AD151" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -19284,7 +19284,7 @@
       </c>
       <c r="P152" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q152" s="2" t="inlineStr">
@@ -19333,12 +19333,12 @@
       </c>
       <c r="AC152" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AD152" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -19404,7 +19404,7 @@
       </c>
       <c r="P153" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q153" s="2" t="inlineStr">
@@ -19453,12 +19453,12 @@
       </c>
       <c r="AC153" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>131.3</t>
         </is>
       </c>
       <c r="AD153" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -19528,7 +19528,7 @@
       </c>
       <c r="P154" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q154" s="2" t="inlineStr">
@@ -19572,17 +19572,17 @@
       </c>
       <c r="AB154" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC154" s="2" t="inlineStr">
         <is>
-          <t>134.8</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AD154" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -19652,7 +19652,7 @@
       </c>
       <c r="P155" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q155" s="2" t="inlineStr">
@@ -19701,12 +19701,12 @@
       </c>
       <c r="AC155" s="2" t="inlineStr">
         <is>
-          <t>130.8</t>
+          <t>132.2</t>
         </is>
       </c>
       <c r="AD155" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -19776,7 +19776,7 @@
       </c>
       <c r="P156" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q156" s="2" t="inlineStr">
@@ -19825,7 +19825,7 @@
       </c>
       <c r="AC156" s="2" t="inlineStr">
         <is>
-          <t>130.2</t>
+          <t>128.8</t>
         </is>
       </c>
       <c r="AD156" s="2" t="inlineStr">
@@ -19900,7 +19900,7 @@
       </c>
       <c r="P157" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q157" s="2" t="inlineStr">
@@ -19944,17 +19944,17 @@
       </c>
       <c r="AB157" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC157" s="2" t="inlineStr">
         <is>
-          <t>133.8</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AD157" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -20078,7 +20078,7 @@
       </c>
       <c r="AD158" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -20148,7 +20148,7 @@
       </c>
       <c r="P159" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q159" s="2" t="inlineStr">
@@ -20197,12 +20197,12 @@
       </c>
       <c r="AC159" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AD159" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -20326,7 +20326,7 @@
       </c>
       <c r="AD160" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -20516,7 +20516,7 @@
       </c>
       <c r="P162" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q162" s="2" t="inlineStr">
@@ -20560,17 +20560,17 @@
       </c>
       <c r="AB162" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC162" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>136.2</t>
         </is>
       </c>
       <c r="AD162" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -20694,7 +20694,7 @@
       </c>
       <c r="AD163" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -20818,7 +20818,7 @@
       </c>
       <c r="AD164" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -21066,7 +21066,7 @@
       </c>
       <c r="AD166" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -21356,12 +21356,12 @@
       </c>
       <c r="H169" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I169" s="2" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>20:36</t>
         </is>
       </c>
       <c r="J169" s="2" t="inlineStr">
@@ -21373,10 +21373,14 @@
       <c r="L169" s="2" t="inlineStr"/>
       <c r="M169" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：20:20采样，终点ETA 15分钟</t>
-        </is>
-      </c>
-      <c r="N169" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N169" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O169" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -21384,7 +21388,7 @@
       </c>
       <c r="P169" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q169" s="2" t="inlineStr">
@@ -21408,12 +21412,12 @@
       </c>
       <c r="X169" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y169" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z169" s="2" t="inlineStr">
@@ -21428,17 +21432,17 @@
       </c>
       <c r="AB169" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC169" s="2" t="inlineStr">
         <is>
-          <t>135.3</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="AD169" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -21481,24 +21485,24 @@
       </c>
       <c r="I170" s="2" t="inlineStr">
         <is>
-          <t>20:45</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="J170" s="2" t="inlineStr">
         <is>
-          <t>140分钟</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="K170" s="2" t="inlineStr"/>
       <c r="L170" s="2" t="inlineStr"/>
       <c r="M170" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N170" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O170" s="2" t="inlineStr">
@@ -21508,7 +21512,7 @@
       </c>
       <c r="P170" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q170" s="2" t="inlineStr">
@@ -21557,12 +21561,12 @@
       </c>
       <c r="AC170" s="2" t="inlineStr">
         <is>
-          <t>146.7</t>
+          <t>145.3</t>
         </is>
       </c>
       <c r="AD170" s="2" t="inlineStr">
         <is>
-          <t>27/29</t>
+          <t>28/29</t>
         </is>
       </c>
     </row>
@@ -21600,27 +21604,31 @@
       </c>
       <c r="H171" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I171" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:55</t>
         </is>
       </c>
       <c r="J171" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="K171" s="2" t="inlineStr"/>
       <c r="L171" s="2" t="inlineStr"/>
       <c r="M171" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N171" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N171" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O171" s="2" t="inlineStr">
         <is>
           <t>17:50</t>
@@ -21628,7 +21636,7 @@
       </c>
       <c r="P171" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q171" s="2" t="inlineStr">
@@ -21652,17 +21660,17 @@
       </c>
       <c r="X171" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y171" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z171" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA171" s="2" t="inlineStr">
@@ -21672,13 +21680,17 @@
       </c>
       <c r="AB171" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC171" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC171" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
       <c r="AD171" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -21716,27 +21728,31 @@
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I172" s="2" t="inlineStr">
         <is>
-          <t>20:59</t>
+          <t>20:56</t>
         </is>
       </c>
       <c r="J172" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="K172" s="2" t="inlineStr"/>
       <c r="L172" s="2" t="inlineStr"/>
       <c r="M172" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：20:10采样，终点ETA 49分钟</t>
-        </is>
-      </c>
-      <c r="N172" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N172" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O172" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -21744,7 +21760,7 @@
       </c>
       <c r="P172" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q172" s="2" t="inlineStr">
@@ -21768,17 +21784,17 @@
       </c>
       <c r="X172" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y172" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z172" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA172" s="2" t="inlineStr">
@@ -21788,17 +21804,17 @@
       </c>
       <c r="AB172" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC172" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AD172" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -21836,24 +21852,24 @@
       </c>
       <c r="H173" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I173" s="2" t="inlineStr">
         <is>
-          <t>21:04</t>
+          <t>21:03</t>
         </is>
       </c>
       <c r="J173" s="2" t="inlineStr">
         <is>
-          <t>125分钟</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="K173" s="2" t="inlineStr"/>
       <c r="L173" s="2" t="inlineStr"/>
       <c r="M173" s="2" t="inlineStr">
         <is>
-          <t>20:10采样：该车到重点站沪南路北中路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数52分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N173" s="2" t="inlineStr">
@@ -21868,7 +21884,7 @@
       </c>
       <c r="P173" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q173" s="2" t="inlineStr">
@@ -21892,12 +21908,12 @@
       </c>
       <c r="X173" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y173" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z173" s="2" t="inlineStr">
@@ -21917,12 +21933,12 @@
       </c>
       <c r="AC173" s="2" t="inlineStr">
         <is>
-          <t>135.2</t>
+          <t>134.8</t>
         </is>
       </c>
       <c r="AD173" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -21955,36 +21971,32 @@
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程43%处后消失；随后反向物理轨迹由seq28推进至seq62，推进34站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I174" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J174" s="2" t="inlineStr">
         <is>
-          <t>131分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K174" s="2" t="inlineStr"/>
       <c r="L174" s="2" t="inlineStr"/>
       <c r="M174" s="2" t="inlineStr">
         <is>
-          <t>20:01采样：该车到重点站丁香路锦绣路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数79分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N174" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N174" s="2" t="inlineStr"/>
       <c r="O174" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -21992,7 +22004,7 @@
       </c>
       <c r="P174" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q174" s="2" t="inlineStr">
@@ -22000,10 +22012,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R174" s="2" t="inlineStr"/>
-      <c r="S174" s="2" t="inlineStr"/>
-      <c r="T174" s="2" t="inlineStr"/>
-      <c r="U174" s="2" t="inlineStr"/>
+      <c r="R174" s="2" t="inlineStr">
+        <is>
+          <t>丁香路锦绣路</t>
+        </is>
+      </c>
+      <c r="S174" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="T174" s="2" t="inlineStr">
+        <is>
+          <t>20:13</t>
+        </is>
+      </c>
+      <c r="U174" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq29映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±8分钟；反向位置物理seq28（站名待映射） ETA 1分钟参与校验</t>
+        </is>
+      </c>
       <c r="V174" s="2" t="inlineStr">
         <is>
           <t>19:10</t>
@@ -22016,17 +22044,17 @@
       </c>
       <c r="X174" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y174" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z174" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA174" s="2" t="inlineStr">
@@ -22036,17 +22064,17 @@
       </c>
       <c r="AB174" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC174" s="2" t="inlineStr">
         <is>
-          <t>134.8</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AD174" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -22084,29 +22112,29 @@
       </c>
       <c r="H175" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I175" s="2" t="inlineStr">
         <is>
-          <t>21:18</t>
+          <t>21:25</t>
         </is>
       </c>
       <c r="J175" s="2" t="inlineStr">
         <is>
-          <t>124分钟</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="K175" s="2" t="inlineStr"/>
       <c r="L175" s="2" t="inlineStr"/>
       <c r="M175" s="2" t="inlineStr">
         <is>
-          <t>20:20采样：该车到重点站迎春路金松路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数57分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="N175" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O175" s="2" t="inlineStr">
@@ -22116,7 +22144,7 @@
       </c>
       <c r="P175" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q175" s="2" t="inlineStr">
@@ -22140,12 +22168,12 @@
       </c>
       <c r="X175" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y175" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z175" s="2" t="inlineStr">
@@ -22165,12 +22193,12 @@
       </c>
       <c r="AC175" s="2" t="inlineStr">
         <is>
-          <t>130.8</t>
+          <t>132.2</t>
         </is>
       </c>
       <c r="AD175" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -22208,7 +22236,7 @@
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I176" s="2" t="inlineStr">
@@ -22225,12 +22253,12 @@
       <c r="L176" s="2" t="inlineStr"/>
       <c r="M176" s="2" t="inlineStr">
         <is>
-          <t>20:20采样：该车到重点站浦建路锦绣路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数63分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N176" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O176" s="2" t="inlineStr">
@@ -22240,7 +22268,7 @@
       </c>
       <c r="P176" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q176" s="2" t="inlineStr">
@@ -22264,12 +22292,12 @@
       </c>
       <c r="X176" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y176" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z176" s="2" t="inlineStr">
@@ -22294,7 +22322,7 @@
       </c>
       <c r="AD176" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -22337,19 +22365,19 @@
       </c>
       <c r="I177" s="2" t="inlineStr">
         <is>
-          <t>21:39</t>
+          <t>21:35</t>
         </is>
       </c>
       <c r="J177" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="K177" s="2" t="inlineStr"/>
       <c r="L177" s="2" t="inlineStr"/>
       <c r="M177" s="2" t="inlineStr">
         <is>
-          <t>20:20采样：该车到重点站锦绣路花木路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数71分钟，约±5分钟</t>
+          <t>20:40采样：该车到重点站云山路碧云路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数51分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N177" s="2" t="inlineStr">
@@ -22364,7 +22392,7 @@
       </c>
       <c r="P177" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q177" s="2" t="inlineStr">
@@ -22413,12 +22441,12 @@
       </c>
       <c r="AC177" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>131.3</t>
         </is>
       </c>
       <c r="AD177" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -22451,36 +22479,32 @@
       </c>
       <c r="G178" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程44%处后消失；随后反向物理轨迹由seq28推进至seq49，推进21站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I178" s="2" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J178" s="2" t="inlineStr">
         <is>
-          <t>126分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K178" s="2" t="inlineStr"/>
       <c r="L178" s="2" t="inlineStr"/>
       <c r="M178" s="2" t="inlineStr">
         <is>
-          <t>20:20采样：该车到重点站迎春路长柳路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数72分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N178" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N178" s="2" t="inlineStr"/>
       <c r="O178" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -22488,7 +22512,7 @@
       </c>
       <c r="P178" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q178" s="2" t="inlineStr">
@@ -22496,10 +22520,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R178" s="2" t="inlineStr"/>
-      <c r="S178" s="2" t="inlineStr"/>
-      <c r="T178" s="2" t="inlineStr"/>
-      <c r="U178" s="2" t="inlineStr"/>
+      <c r="R178" s="2" t="inlineStr">
+        <is>
+          <t>丁香路锦绣路</t>
+        </is>
+      </c>
+      <c r="S178" s="2" t="inlineStr">
+        <is>
+          <t>20:23</t>
+        </is>
+      </c>
+      <c r="T178" s="2" t="inlineStr">
+        <is>
+          <t>20:32</t>
+        </is>
+      </c>
+      <c r="U178" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq29映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±8分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="V178" s="2" t="inlineStr">
         <is>
           <t>19:30</t>
@@ -22512,17 +22552,17 @@
       </c>
       <c r="X178" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y178" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z178" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA178" s="2" t="inlineStr">
@@ -22532,17 +22572,17 @@
       </c>
       <c r="AB178" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC178" s="2" t="inlineStr">
         <is>
-          <t>133.8</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AD178" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -22585,19 +22625,19 @@
       </c>
       <c r="I179" s="2" t="inlineStr">
         <is>
-          <t>21:46</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="J179" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>121分钟</t>
         </is>
       </c>
       <c r="K179" s="2" t="inlineStr"/>
       <c r="L179" s="2" t="inlineStr"/>
       <c r="M179" s="2" t="inlineStr">
         <is>
-          <t>20:20采样：该车到重点站沪南路高科西路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数78分钟，约±5分钟</t>
+          <t>21:20采样：该车到重点站东波路莱阳路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数16分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N179" s="2" t="inlineStr">
@@ -22612,7 +22652,7 @@
       </c>
       <c r="P179" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q179" s="2" t="inlineStr">
@@ -22661,7 +22701,7 @@
       </c>
       <c r="AC179" s="2" t="inlineStr">
         <is>
-          <t>130.2</t>
+          <t>128.8</t>
         </is>
       </c>
       <c r="AD179" s="2" t="inlineStr">
@@ -22704,29 +22744,29 @@
       </c>
       <c r="H180" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I180" s="2" t="inlineStr">
         <is>
-          <t>21:56</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="J180" s="2" t="inlineStr">
         <is>
-          <t>137分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="K180" s="2" t="inlineStr"/>
       <c r="L180" s="2" t="inlineStr"/>
       <c r="M180" s="2" t="inlineStr">
         <is>
-          <t>20:20采样：该车到重点站白桦路明月路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数87分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N180" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O180" s="2" t="inlineStr">
@@ -22736,7 +22776,7 @@
       </c>
       <c r="P180" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q180" s="2" t="inlineStr">
@@ -22760,12 +22800,12 @@
       </c>
       <c r="X180" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y180" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z180" s="2" t="inlineStr">
@@ -22785,12 +22825,12 @@
       </c>
       <c r="AC180" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AD180" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -22833,19 +22873,19 @@
       </c>
       <c r="I181" s="2" t="inlineStr">
         <is>
-          <t>22:17</t>
+          <t>22:07</t>
         </is>
       </c>
       <c r="J181" s="2" t="inlineStr">
         <is>
-          <t>138分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="K181" s="2" t="inlineStr"/>
       <c r="L181" s="2" t="inlineStr"/>
       <c r="M181" s="2" t="inlineStr">
         <is>
-          <t>20:20采样：该车到重点站博兴路兰城路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数115分钟，约±5分钟</t>
+          <t>21:20采样：该车到重点站周东路川周公路 ETA 30分钟；叠加该车自身同类时段从该站到终点历史中位数17分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N181" s="2" t="inlineStr">
@@ -22860,7 +22900,7 @@
       </c>
       <c r="P181" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q181" s="2" t="inlineStr">
@@ -22909,12 +22949,12 @@
       </c>
       <c r="AC181" s="2" t="inlineStr">
         <is>
-          <t>140.8</t>
+          <t>138.2</t>
         </is>
       </c>
       <c r="AD181" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -22957,19 +22997,19 @@
       </c>
       <c r="I182" s="2" t="inlineStr">
         <is>
-          <t>22:25</t>
+          <t>22:12</t>
         </is>
       </c>
       <c r="J182" s="2" t="inlineStr">
         <is>
-          <t>140分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="K182" s="2" t="inlineStr"/>
       <c r="L182" s="2" t="inlineStr"/>
       <c r="M182" s="2" t="inlineStr">
         <is>
-          <t>20:20采样：该车到重点站川周公路康沈路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数123分钟，约±5分钟</t>
+          <t>21:20采样：该车到重点站云山路碧云路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数51分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N182" s="2" t="inlineStr">
@@ -22984,7 +23024,7 @@
       </c>
       <c r="P182" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q182" s="2" t="inlineStr">
@@ -23033,12 +23073,12 @@
       </c>
       <c r="AC182" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AD182" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -23081,22 +23121,26 @@
       </c>
       <c r="I183" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="J183" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="K183" s="2" t="inlineStr"/>
       <c r="L183" s="2" t="inlineStr"/>
       <c r="M183" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N183" s="2" t="inlineStr"/>
+          <t>21:20采样：该车到重点站迎春路金松路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数69分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N183" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O183" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -23104,7 +23148,7 @@
       </c>
       <c r="P183" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q183" s="2" t="inlineStr">
@@ -23128,17 +23172,17 @@
       </c>
       <c r="X183" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y183" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z183" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA183" s="2" t="inlineStr">
@@ -23148,17 +23192,17 @@
       </c>
       <c r="AB183" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC183" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>136.2</t>
         </is>
       </c>
       <c r="AD183" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -23201,22 +23245,26 @@
       </c>
       <c r="I184" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="J184" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="K184" s="2" t="inlineStr"/>
       <c r="L184" s="2" t="inlineStr"/>
       <c r="M184" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N184" s="2" t="inlineStr"/>
+          <t>21:20采样：该车到重点站沪南路华夏西路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数92分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N184" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O184" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -23224,7 +23272,7 @@
       </c>
       <c r="P184" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q184" s="2" t="inlineStr">
@@ -23248,17 +23296,17 @@
       </c>
       <c r="X184" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y184" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z184" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA184" s="2" t="inlineStr">
@@ -23268,17 +23316,17 @@
       </c>
       <c r="AB184" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC184" s="2" t="inlineStr">
         <is>
-          <t>135.3</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="AD184" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -23402,7 +23450,7 @@
       </c>
       <c r="AD185" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -23968,7 +24016,7 @@
       </c>
       <c r="P190" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q190" s="2" t="inlineStr">
@@ -24017,7 +24065,7 @@
       </c>
       <c r="AC190" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AD190" s="2" t="inlineStr">
@@ -24270,7 +24318,7 @@
       </c>
       <c r="AD192" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -24340,7 +24388,7 @@
       </c>
       <c r="P193" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q193" s="2" t="inlineStr">
@@ -24389,12 +24437,12 @@
       </c>
       <c r="AC193" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AD193" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -24464,7 +24512,7 @@
       </c>
       <c r="P194" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q194" s="2" t="inlineStr">
@@ -24513,12 +24561,12 @@
       </c>
       <c r="AC194" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AD194" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -24832,7 +24880,7 @@
       </c>
       <c r="P197" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q197" s="2" t="inlineStr">
@@ -24881,12 +24929,12 @@
       </c>
       <c r="AC197" s="2" t="inlineStr">
         <is>
-          <t>84.9</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AD197" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -25320,7 +25368,7 @@
       </c>
       <c r="P201" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q201" s="2" t="inlineStr">
@@ -25369,7 +25417,7 @@
       </c>
       <c r="AC201" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AD201" s="2" t="inlineStr">
@@ -25444,7 +25492,7 @@
       </c>
       <c r="P202" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q202" s="2" t="inlineStr">
@@ -25493,7 +25541,7 @@
       </c>
       <c r="AC202" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AD202" s="2" t="inlineStr">
@@ -25564,7 +25612,7 @@
       </c>
       <c r="P203" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q203" s="2" t="inlineStr">
@@ -25613,7 +25661,7 @@
       </c>
       <c r="AC203" s="2" t="inlineStr">
         <is>
-          <t>81.1</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AD203" s="2" t="inlineStr">
@@ -25684,7 +25732,7 @@
       </c>
       <c r="P204" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q204" s="2" t="inlineStr">
@@ -25733,7 +25781,7 @@
       </c>
       <c r="AC204" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AD204" s="2" t="inlineStr">
@@ -25932,7 +25980,7 @@
       </c>
       <c r="P206" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q206" s="2" t="inlineStr">
@@ -25981,12 +26029,12 @@
       </c>
       <c r="AC206" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AD206" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -26110,7 +26158,7 @@
       </c>
       <c r="AD207" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -26176,7 +26224,7 @@
       </c>
       <c r="P208" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q208" s="2" t="inlineStr">
@@ -26225,12 +26273,12 @@
       </c>
       <c r="AC208" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AD208" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -26796,7 +26844,7 @@
       </c>
       <c r="P213" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q213" s="2" t="inlineStr">
@@ -26845,12 +26893,12 @@
       </c>
       <c r="AC213" s="2" t="inlineStr">
         <is>
-          <t>84.9</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AD213" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -26920,7 +26968,7 @@
       </c>
       <c r="P214" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q214" s="2" t="inlineStr">
@@ -26969,7 +27017,7 @@
       </c>
       <c r="AC214" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AD214" s="2" t="inlineStr">
@@ -27044,7 +27092,7 @@
       </c>
       <c r="P215" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q215" s="2" t="inlineStr">
@@ -27093,7 +27141,7 @@
       </c>
       <c r="AC215" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AD215" s="2" t="inlineStr">
@@ -27168,7 +27216,7 @@
       </c>
       <c r="P216" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q216" s="2" t="inlineStr">
@@ -27217,7 +27265,7 @@
       </c>
       <c r="AC216" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AD216" s="2" t="inlineStr">
@@ -27346,7 +27394,7 @@
       </c>
       <c r="AD217" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -27416,7 +27464,7 @@
       </c>
       <c r="P218" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q218" s="2" t="inlineStr">
@@ -27465,7 +27513,7 @@
       </c>
       <c r="AC218" s="2" t="inlineStr">
         <is>
-          <t>81.1</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AD218" s="2" t="inlineStr">
@@ -27540,7 +27588,7 @@
       </c>
       <c r="P219" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q219" s="2" t="inlineStr">
@@ -27589,12 +27637,12 @@
       </c>
       <c r="AC219" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AD219" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -27912,7 +27960,7 @@
       </c>
       <c r="P222" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q222" s="2" t="inlineStr">
@@ -27961,12 +28009,12 @@
       </c>
       <c r="AC222" s="2" t="inlineStr">
         <is>
-          <t>84.9</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AD222" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -28160,7 +28208,7 @@
       </c>
       <c r="P224" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q224" s="2" t="inlineStr">
@@ -28209,7 +28257,7 @@
       </c>
       <c r="AC224" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AD224" s="2" t="inlineStr">
@@ -28404,7 +28452,7 @@
       </c>
       <c r="P226" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q226" s="2" t="inlineStr">
@@ -28453,7 +28501,7 @@
       </c>
       <c r="AC226" s="2" t="inlineStr">
         <is>
-          <t>81.1</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AD226" s="2" t="inlineStr">
@@ -28528,7 +28576,7 @@
       </c>
       <c r="P227" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q227" s="2" t="inlineStr">
@@ -28577,7 +28625,7 @@
       </c>
       <c r="AC227" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AD227" s="2" t="inlineStr">
@@ -28776,7 +28824,7 @@
       </c>
       <c r="P229" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q229" s="2" t="inlineStr">
@@ -28825,12 +28873,12 @@
       </c>
       <c r="AC229" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AD229" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -29392,7 +29440,7 @@
       </c>
       <c r="P234" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q234" s="2" t="inlineStr">
@@ -29441,7 +29489,7 @@
       </c>
       <c r="AC234" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AD234" s="2" t="inlineStr">
@@ -29516,7 +29564,7 @@
       </c>
       <c r="P235" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q235" s="2" t="inlineStr">
@@ -29565,12 +29613,12 @@
       </c>
       <c r="AC235" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AD235" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -29640,7 +29688,7 @@
       </c>
       <c r="P236" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q236" s="2" t="inlineStr">
@@ -29689,12 +29737,12 @@
       </c>
       <c r="AC236" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AD236" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -29764,7 +29812,7 @@
       </c>
       <c r="P237" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q237" s="2" t="inlineStr">
@@ -29813,12 +29861,12 @@
       </c>
       <c r="AC237" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AD237" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -30252,7 +30300,7 @@
       </c>
       <c r="P241" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q241" s="2" t="inlineStr">
@@ -30301,12 +30349,12 @@
       </c>
       <c r="AC241" s="2" t="inlineStr">
         <is>
-          <t>84.9</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AD241" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -30500,7 +30548,7 @@
       </c>
       <c r="P243" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q243" s="2" t="inlineStr">
@@ -30549,7 +30597,7 @@
       </c>
       <c r="AC243" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AD243" s="2" t="inlineStr">
@@ -30624,7 +30672,7 @@
       </c>
       <c r="P244" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q244" s="2" t="inlineStr">
@@ -30673,12 +30721,12 @@
       </c>
       <c r="AC244" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AD244" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -30872,7 +30920,7 @@
       </c>
       <c r="P246" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q246" s="2" t="inlineStr">
@@ -30921,7 +30969,7 @@
       </c>
       <c r="AC246" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AD246" s="2" t="inlineStr">
@@ -30996,7 +31044,7 @@
       </c>
       <c r="P247" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q247" s="2" t="inlineStr">
@@ -31045,12 +31093,12 @@
       </c>
       <c r="AC247" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AD247" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -31120,7 +31168,7 @@
       </c>
       <c r="P248" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q248" s="2" t="inlineStr">
@@ -31169,7 +31217,7 @@
       </c>
       <c r="AC248" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AD248" s="2" t="inlineStr">
@@ -31244,7 +31292,7 @@
       </c>
       <c r="P249" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q249" s="2" t="inlineStr">
@@ -31293,7 +31341,7 @@
       </c>
       <c r="AC249" s="2" t="inlineStr">
         <is>
-          <t>81.1</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AD249" s="2" t="inlineStr">
@@ -31488,7 +31536,7 @@
       </c>
       <c r="P251" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q251" s="2" t="inlineStr">
@@ -31537,12 +31585,12 @@
       </c>
       <c r="AC251" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AD251" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -31914,7 +31962,7 @@
       </c>
       <c r="AD254" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -31980,7 +32028,7 @@
       </c>
       <c r="P255" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q255" s="2" t="inlineStr">
@@ -32029,12 +32077,12 @@
       </c>
       <c r="AC255" s="2" t="inlineStr">
         <is>
-          <t>84.9</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AD255" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -32220,7 +32268,7 @@
       </c>
       <c r="P257" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q257" s="2" t="inlineStr">
@@ -32269,7 +32317,7 @@
       </c>
       <c r="AC257" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AD257" s="2" t="inlineStr">
@@ -32588,7 +32636,7 @@
       </c>
       <c r="P260" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q260" s="2" t="inlineStr">
@@ -32637,7 +32685,7 @@
       </c>
       <c r="AC260" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AD260" s="2" t="inlineStr">
@@ -32712,7 +32760,7 @@
       </c>
       <c r="P261" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q261" s="2" t="inlineStr">
@@ -32761,12 +32809,12 @@
       </c>
       <c r="AC261" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AD261" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -32836,7 +32884,7 @@
       </c>
       <c r="P262" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q262" s="2" t="inlineStr">
@@ -32885,7 +32933,7 @@
       </c>
       <c r="AC262" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AD262" s="2" t="inlineStr">
@@ -32960,7 +33008,7 @@
       </c>
       <c r="P263" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q263" s="2" t="inlineStr">
@@ -33009,7 +33057,7 @@
       </c>
       <c r="AC263" s="2" t="inlineStr">
         <is>
-          <t>81.1</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AD263" s="2" t="inlineStr">
@@ -33084,7 +33132,7 @@
       </c>
       <c r="P264" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q264" s="2" t="inlineStr">
@@ -33133,12 +33181,12 @@
       </c>
       <c r="AC264" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AD264" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -33208,7 +33256,7 @@
       </c>
       <c r="P265" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q265" s="2" t="inlineStr">
@@ -33257,12 +33305,12 @@
       </c>
       <c r="AC265" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AD265" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -33758,7 +33806,7 @@
       </c>
       <c r="AD269" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -33828,7 +33876,7 @@
       </c>
       <c r="P270" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q270" s="2" t="inlineStr">
@@ -33877,12 +33925,12 @@
       </c>
       <c r="AC270" s="2" t="inlineStr">
         <is>
-          <t>84.9</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AD270" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -34076,7 +34124,7 @@
       </c>
       <c r="P272" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q272" s="2" t="inlineStr">
@@ -34125,7 +34173,7 @@
       </c>
       <c r="AC272" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AD272" s="2" t="inlineStr">
@@ -34421,12 +34469,12 @@
       </c>
       <c r="I275" s="2" t="inlineStr">
         <is>
-          <t>20:38</t>
+          <t>20:36</t>
         </is>
       </c>
       <c r="J275" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="K275" s="2" t="inlineStr"/>
@@ -34448,7 +34496,7 @@
       </c>
       <c r="P275" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q275" s="2" t="inlineStr">
@@ -34497,7 +34545,7 @@
       </c>
       <c r="AC275" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AD275" s="2" t="inlineStr">
@@ -34545,24 +34593,24 @@
       </c>
       <c r="I276" s="2" t="inlineStr">
         <is>
-          <t>20:36</t>
+          <t>20:34</t>
         </is>
       </c>
       <c r="J276" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="K276" s="2" t="inlineStr"/>
       <c r="L276" s="2" t="inlineStr"/>
       <c r="M276" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N276" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O276" s="2" t="inlineStr">
@@ -34572,7 +34620,7 @@
       </c>
       <c r="P276" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q276" s="2" t="inlineStr">
@@ -34621,12 +34669,12 @@
       </c>
       <c r="AC276" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AD276" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -34669,26 +34717,22 @@
       </c>
       <c r="I277" s="2" t="inlineStr">
         <is>
-          <t>20:49</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="J277" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="K277" s="2" t="inlineStr"/>
       <c r="L277" s="2" t="inlineStr"/>
       <c r="M277" s="2" t="inlineStr">
         <is>
-          <t>20:20采样：该车到重点站云山路灵山路 ETA 13分钟；叠加该车自身同类时段从该站到终点历史中位数16分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N277" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：20:30采样，终点ETA 13分钟</t>
+        </is>
+      </c>
+      <c r="N277" s="2" t="inlineStr"/>
       <c r="O277" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -34696,7 +34740,7 @@
       </c>
       <c r="P277" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q277" s="2" t="inlineStr">
@@ -34725,7 +34769,7 @@
       </c>
       <c r="Y277" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Z277" s="2" t="inlineStr">
@@ -34745,7 +34789,7 @@
       </c>
       <c r="AC277" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AD277" s="2" t="inlineStr">
@@ -34912,27 +34956,31 @@
       </c>
       <c r="H279" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I279" s="2" t="inlineStr">
         <is>
-          <t>20:59</t>
+          <t>20:55</t>
         </is>
       </c>
       <c r="J279" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="K279" s="2" t="inlineStr"/>
       <c r="L279" s="2" t="inlineStr"/>
       <c r="M279" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：20:20采样，终点ETA 39分钟</t>
-        </is>
-      </c>
-      <c r="N279" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N279" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O279" s="2" t="inlineStr">
         <is>
           <t>07:10</t>
@@ -34940,7 +34988,7 @@
       </c>
       <c r="P279" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q279" s="2" t="inlineStr">
@@ -34964,12 +35012,12 @@
       </c>
       <c r="X279" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y279" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z279" s="2" t="inlineStr">
@@ -34989,12 +35037,12 @@
       </c>
       <c r="AC279" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AD279" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -35118,7 +35166,7 @@
       </c>
       <c r="AD280" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -35156,24 +35204,24 @@
       </c>
       <c r="H281" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I281" s="2" t="inlineStr">
         <is>
-          <t>21:02</t>
+          <t>20:54</t>
         </is>
       </c>
       <c r="J281" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="K281" s="2" t="inlineStr"/>
       <c r="L281" s="2" t="inlineStr"/>
       <c r="M281" s="2" t="inlineStr">
         <is>
-          <t>同车下一次反向发车21:10，减去该车自身同类时段历史终点停站中位数8分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N281" s="2" t="inlineStr">
@@ -35188,7 +35236,7 @@
       </c>
       <c r="P281" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q281" s="2" t="inlineStr">
@@ -35212,12 +35260,12 @@
       </c>
       <c r="X281" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y281" s="2" t="inlineStr">
         <is>
-          <t>同车反向发车反推</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z281" s="2" t="inlineStr">
@@ -35237,7 +35285,7 @@
       </c>
       <c r="AC281" s="2" t="inlineStr">
         <is>
-          <t>81.1</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AD281" s="2" t="inlineStr">
@@ -35280,29 +35328,29 @@
       </c>
       <c r="H282" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I282" s="2" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="J282" s="2" t="inlineStr">
         <is>
-          <t>92分钟</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="K282" s="2" t="inlineStr"/>
       <c r="L282" s="2" t="inlineStr"/>
       <c r="M282" s="2" t="inlineStr">
         <is>
-          <t>同车下一次反向发车21:40，减去该车自身同类时段历史终点停站中位数10分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N282" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O282" s="2" t="inlineStr">
@@ -35312,7 +35360,7 @@
       </c>
       <c r="P282" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q282" s="2" t="inlineStr">
@@ -35336,12 +35384,12 @@
       </c>
       <c r="X282" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y282" s="2" t="inlineStr">
         <is>
-          <t>同车反向发车反推</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z282" s="2" t="inlineStr">
@@ -35361,12 +35409,12 @@
       </c>
       <c r="AC282" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AD282" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -35404,29 +35452,29 @@
       </c>
       <c r="H283" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I283" s="2" t="inlineStr">
         <is>
-          <t>21:29</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="J283" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="K283" s="2" t="inlineStr"/>
       <c r="L283" s="2" t="inlineStr"/>
       <c r="M283" s="2" t="inlineStr">
         <is>
-          <t>20:20采样：该车到重点站五莲路凌河路 ETA 20分钟；叠加该车自身同类时段从该站到终点历史中位数49分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N283" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O283" s="2" t="inlineStr">
@@ -35436,7 +35484,7 @@
       </c>
       <c r="P283" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q283" s="2" t="inlineStr">
@@ -35460,12 +35508,12 @@
       </c>
       <c r="X283" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y283" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z283" s="2" t="inlineStr">
@@ -35485,12 +35533,12 @@
       </c>
       <c r="AC283" s="2" t="inlineStr">
         <is>
-          <t>84.9</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AD283" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -35528,29 +35576,29 @@
       </c>
       <c r="H284" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I284" s="2" t="inlineStr">
         <is>
-          <t>21:58</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="J284" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="K284" s="2" t="inlineStr"/>
       <c r="L284" s="2" t="inlineStr"/>
       <c r="M284" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数78分钟估算，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N284" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O284" s="2" t="inlineStr">
@@ -35560,7 +35608,7 @@
       </c>
       <c r="P284" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q284" s="2" t="inlineStr">
@@ -35584,12 +35632,12 @@
       </c>
       <c r="X284" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y284" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z284" s="2" t="inlineStr">
@@ -35609,7 +35657,7 @@
       </c>
       <c r="AC284" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AD284" s="2" t="inlineStr">
@@ -35657,24 +35705,24 @@
       </c>
       <c r="I285" s="2" t="inlineStr">
         <is>
-          <t>22:31</t>
+          <t>22:26</t>
         </is>
       </c>
       <c r="J285" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="K285" s="2" t="inlineStr"/>
       <c r="L285" s="2" t="inlineStr"/>
       <c r="M285" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数81分钟估算，约±7分钟</t>
+          <t>21:20采样：该车到重点站金杨路枣庄路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数60分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N285" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O285" s="2" t="inlineStr">
@@ -35684,7 +35732,7 @@
       </c>
       <c r="P285" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q285" s="2" t="inlineStr">
@@ -35713,7 +35761,7 @@
       </c>
       <c r="Y285" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z285" s="2" t="inlineStr">
@@ -35733,7 +35781,7 @@
       </c>
       <c r="AC285" s="2" t="inlineStr">
         <is>
-          <t>81.1</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AD285" s="2" t="inlineStr">
@@ -35808,7 +35856,7 @@
       </c>
       <c r="P286" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q286" s="2" t="inlineStr">
@@ -35857,12 +35905,12 @@
       </c>
       <c r="AC286" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AD286" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-19-operations.xlsx
+++ b/data/export/2026-09-19-operations.xlsx
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -729,12 +729,12 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -982,7 +982,7 @@
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AD8" s="2" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1969,12 +1969,12 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -2292,7 +2292,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -2842,7 +2842,7 @@
       </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -2912,7 +2912,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2956,12 +2956,12 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AD20" s="2" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -3904,7 +3904,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AD28" s="2" t="inlineStr">
@@ -4082,7 +4082,7 @@
       </c>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -4454,7 +4454,7 @@
       </c>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -4950,7 +4950,7 @@
       </c>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -5392,7 +5392,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -5764,7 +5764,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5813,12 +5813,12 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -6066,7 +6066,7 @@
       </c>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -6314,7 +6314,7 @@
       </c>
       <c r="AD47" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -6562,7 +6562,7 @@
       </c>
       <c r="AD49" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -6632,7 +6632,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AD50" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="AD52" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -7182,7 +7182,7 @@
       </c>
       <c r="AD54" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -7252,7 +7252,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -7550,7 +7550,7 @@
       </c>
       <c r="AD57" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -7616,7 +7616,7 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7660,12 +7660,12 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AD58" s="2" t="inlineStr">
@@ -7740,7 +7740,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7789,12 +7789,12 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AD59" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -8236,7 +8236,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -8414,7 +8414,7 @@
       </c>
       <c r="AD64" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -8732,7 +8732,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8776,12 +8776,12 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AD67" s="2" t="inlineStr">
@@ -8856,7 +8856,7 @@
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8905,12 +8905,12 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AD68" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -9034,7 +9034,7 @@
       </c>
       <c r="AD69" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="AD72" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -9476,7 +9476,7 @@
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -9724,7 +9724,7 @@
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -9768,12 +9768,12 @@
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AD75" s="2" t="inlineStr">
@@ -9902,7 +9902,7 @@
       </c>
       <c r="AD76" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -9972,7 +9972,7 @@
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -10021,12 +10021,12 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AD77" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -10220,7 +10220,7 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -10312,27 +10312,31 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>22:12</t>
+          <t>22:07</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr"/>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：21:21采样，终点ETA 51分钟</t>
-        </is>
-      </c>
-      <c r="N80" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10340,7 +10344,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -10364,17 +10368,17 @@
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA80" s="2" t="inlineStr">
@@ -10384,12 +10388,12 @@
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AD80" s="2" t="inlineStr">
@@ -10432,29 +10436,29 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>22:19</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>64分钟</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr"/>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>21:21采样：该车到重点站唐陆公路春雅路 ETA 31分钟；叠加该车自身同类时段从该站到终点历史中位数38分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O81" s="2" t="inlineStr">
@@ -10464,7 +10468,7 @@
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -10488,12 +10492,12 @@
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr">
@@ -10513,12 +10517,12 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AD81" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10770,7 @@
       </c>
       <c r="AD83" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -10890,7 +10894,7 @@
       </c>
       <c r="AD84" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -11208,7 +11212,7 @@
       </c>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="Q87" s="2" t="inlineStr">
@@ -11257,7 +11261,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>128.8</t>
+          <t>129.8</t>
         </is>
       </c>
       <c r="AD87" s="2" t="inlineStr">
@@ -11840,7 +11844,7 @@
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -11889,12 +11893,12 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>133.8</t>
         </is>
       </c>
       <c r="AD92" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -12018,7 +12022,7 @@
       </c>
       <c r="AD93" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -12088,7 +12092,7 @@
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
@@ -12132,17 +12136,17 @@
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>136.2</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AD94" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -12212,7 +12216,7 @@
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -12266,7 +12270,7 @@
       </c>
       <c r="AD95" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -12514,7 +12518,7 @@
       </c>
       <c r="AD97" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -12584,7 +12588,7 @@
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr">
@@ -12633,7 +12637,7 @@
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>138.2</t>
+          <t>137.8</t>
         </is>
       </c>
       <c r="AD98" s="2" t="inlineStr">
@@ -12708,7 +12712,7 @@
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q99" s="2" t="inlineStr">
@@ -12757,12 +12761,12 @@
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>131.8</t>
         </is>
       </c>
       <c r="AD99" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -13696,7 +13700,7 @@
       </c>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="Q107" s="2" t="inlineStr">
@@ -13750,7 +13754,7 @@
       </c>
       <c r="AD107" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -13874,7 +13878,7 @@
       </c>
       <c r="AD108" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -13998,7 +14002,7 @@
       </c>
       <c r="AD109" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -14316,7 +14320,7 @@
       </c>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="Q112" s="2" t="inlineStr">
@@ -14365,7 +14369,7 @@
       </c>
       <c r="AC112" s="2" t="inlineStr">
         <is>
-          <t>128.8</t>
+          <t>129.8</t>
         </is>
       </c>
       <c r="AD112" s="2" t="inlineStr">
@@ -14944,7 +14948,7 @@
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q117" s="2" t="inlineStr">
@@ -14993,12 +14997,12 @@
       </c>
       <c r="AC117" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>133.8</t>
         </is>
       </c>
       <c r="AD117" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -15122,7 +15126,7 @@
       </c>
       <c r="AD118" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -15192,7 +15196,7 @@
       </c>
       <c r="P119" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q119" s="2" t="inlineStr">
@@ -15236,17 +15240,17 @@
       </c>
       <c r="AB119" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC119" s="2" t="inlineStr">
         <is>
-          <t>136.2</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AD119" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -15494,7 +15498,7 @@
       </c>
       <c r="AD121" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -15564,7 +15568,7 @@
       </c>
       <c r="P122" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="Q122" s="2" t="inlineStr">
@@ -15618,7 +15622,7 @@
       </c>
       <c r="AD122" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -15688,7 +15692,7 @@
       </c>
       <c r="P123" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q123" s="2" t="inlineStr">
@@ -15737,12 +15741,12 @@
       </c>
       <c r="AC123" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>131.8</t>
         </is>
       </c>
       <c r="AD123" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -15936,7 +15940,7 @@
       </c>
       <c r="P125" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q125" s="2" t="inlineStr">
@@ -15985,7 +15989,7 @@
       </c>
       <c r="AC125" s="2" t="inlineStr">
         <is>
-          <t>138.2</t>
+          <t>137.8</t>
         </is>
       </c>
       <c r="AD125" s="2" t="inlineStr">
@@ -16358,7 +16362,7 @@
       </c>
       <c r="AD128" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -16428,7 +16432,7 @@
       </c>
       <c r="P129" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="Q129" s="2" t="inlineStr">
@@ -16482,7 +16486,7 @@
       </c>
       <c r="AD129" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -17354,7 +17358,7 @@
       </c>
       <c r="AD136" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -17672,7 +17676,7 @@
       </c>
       <c r="P139" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q139" s="2" t="inlineStr">
@@ -17721,7 +17725,7 @@
       </c>
       <c r="AC139" s="2" t="inlineStr">
         <is>
-          <t>138.2</t>
+          <t>137.8</t>
         </is>
       </c>
       <c r="AD139" s="2" t="inlineStr">
@@ -18094,7 +18098,7 @@
       </c>
       <c r="AD142" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19218,7 @@
       </c>
       <c r="AD151" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -19284,7 +19288,7 @@
       </c>
       <c r="P152" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="Q152" s="2" t="inlineStr">
@@ -19338,7 +19342,7 @@
       </c>
       <c r="AD152" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -19706,7 +19710,7 @@
       </c>
       <c r="AD155" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -19776,7 +19780,7 @@
       </c>
       <c r="P156" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="Q156" s="2" t="inlineStr">
@@ -19825,7 +19829,7 @@
       </c>
       <c r="AC156" s="2" t="inlineStr">
         <is>
-          <t>128.8</t>
+          <t>129.8</t>
         </is>
       </c>
       <c r="AD156" s="2" t="inlineStr">
@@ -19900,7 +19904,7 @@
       </c>
       <c r="P157" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="Q157" s="2" t="inlineStr">
@@ -19954,7 +19958,7 @@
       </c>
       <c r="AD157" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -20148,7 +20152,7 @@
       </c>
       <c r="P159" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q159" s="2" t="inlineStr">
@@ -20197,12 +20201,12 @@
       </c>
       <c r="AC159" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>133.8</t>
         </is>
       </c>
       <c r="AD159" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -20516,7 +20520,7 @@
       </c>
       <c r="P162" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q162" s="2" t="inlineStr">
@@ -20560,17 +20564,17 @@
       </c>
       <c r="AB162" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC162" s="2" t="inlineStr">
         <is>
-          <t>136.2</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AD162" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -21388,7 +21392,7 @@
       </c>
       <c r="P169" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q169" s="2" t="inlineStr">
@@ -21437,12 +21441,12 @@
       </c>
       <c r="AC169" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>131.8</t>
         </is>
       </c>
       <c r="AD169" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -22198,7 +22202,7 @@
       </c>
       <c r="AD175" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -22322,7 +22326,7 @@
       </c>
       <c r="AD176" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -22484,7 +22488,7 @@
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程44%处后消失；随后反向物理轨迹由seq28推进至seq49，推进21站，达到≥2站确认条件</t>
+          <t>原方向在全程44%处后消失；随后反向物理轨迹由seq28推进至seq61，推进33站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I178" s="2" t="inlineStr">
@@ -22512,7 +22516,7 @@
       </c>
       <c r="P178" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="Q178" s="2" t="inlineStr">
@@ -22582,7 +22586,7 @@
       </c>
       <c r="AD178" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -22620,29 +22624,29 @@
       </c>
       <c r="H179" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I179" s="2" t="inlineStr">
         <is>
-          <t>21:40</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="J179" s="2" t="inlineStr">
         <is>
-          <t>121分钟</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="K179" s="2" t="inlineStr"/>
       <c r="L179" s="2" t="inlineStr"/>
       <c r="M179" s="2" t="inlineStr">
         <is>
-          <t>21:20采样：该车到重点站东波路莱阳路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数16分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N179" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O179" s="2" t="inlineStr">
@@ -22652,7 +22656,7 @@
       </c>
       <c r="P179" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="Q179" s="2" t="inlineStr">
@@ -22676,12 +22680,12 @@
       </c>
       <c r="X179" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y179" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z179" s="2" t="inlineStr">
@@ -22701,7 +22705,7 @@
       </c>
       <c r="AC179" s="2" t="inlineStr">
         <is>
-          <t>128.8</t>
+          <t>129.8</t>
         </is>
       </c>
       <c r="AD179" s="2" t="inlineStr">
@@ -22776,7 +22780,7 @@
       </c>
       <c r="P180" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="Q180" s="2" t="inlineStr">
@@ -22830,7 +22834,7 @@
       </c>
       <c r="AD180" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -22868,29 +22872,29 @@
       </c>
       <c r="H181" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I181" s="2" t="inlineStr">
         <is>
-          <t>22:07</t>
+          <t>22:06</t>
         </is>
       </c>
       <c r="J181" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="K181" s="2" t="inlineStr"/>
       <c r="L181" s="2" t="inlineStr"/>
       <c r="M181" s="2" t="inlineStr">
         <is>
-          <t>21:20采样：该车到重点站周东路川周公路 ETA 30分钟；叠加该车自身同类时段从该站到终点历史中位数17分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N181" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O181" s="2" t="inlineStr">
@@ -22900,7 +22904,7 @@
       </c>
       <c r="P181" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q181" s="2" t="inlineStr">
@@ -22924,12 +22928,12 @@
       </c>
       <c r="X181" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y181" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z181" s="2" t="inlineStr">
@@ -22949,7 +22953,7 @@
       </c>
       <c r="AC181" s="2" t="inlineStr">
         <is>
-          <t>138.2</t>
+          <t>137.8</t>
         </is>
       </c>
       <c r="AD181" s="2" t="inlineStr">
@@ -22997,26 +23001,22 @@
       </c>
       <c r="I182" s="2" t="inlineStr">
         <is>
-          <t>22:12</t>
+          <t>22:09</t>
         </is>
       </c>
       <c r="J182" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="K182" s="2" t="inlineStr"/>
       <c r="L182" s="2" t="inlineStr"/>
       <c r="M182" s="2" t="inlineStr">
         <is>
-          <t>21:20采样：该车到重点站云山路碧云路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数51分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N182" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：21:50采样，终点ETA 19分钟</t>
+        </is>
+      </c>
+      <c r="N182" s="2" t="inlineStr"/>
       <c r="O182" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -23024,7 +23024,7 @@
       </c>
       <c r="P182" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q182" s="2" t="inlineStr">
@@ -23053,7 +23053,7 @@
       </c>
       <c r="Y182" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Z182" s="2" t="inlineStr">
@@ -23073,12 +23073,12 @@
       </c>
       <c r="AC182" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>133.8</t>
         </is>
       </c>
       <c r="AD182" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -23121,26 +23121,22 @@
       </c>
       <c r="I183" s="2" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>22:38</t>
         </is>
       </c>
       <c r="J183" s="2" t="inlineStr">
         <is>
-          <t>134分钟</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="K183" s="2" t="inlineStr"/>
       <c r="L183" s="2" t="inlineStr"/>
       <c r="M183" s="2" t="inlineStr">
         <is>
-          <t>21:20采样：该车到重点站迎春路金松路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数69分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N183" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：21:50采样，终点ETA 48分钟</t>
+        </is>
+      </c>
+      <c r="N183" s="2" t="inlineStr"/>
       <c r="O183" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -23148,7 +23144,7 @@
       </c>
       <c r="P183" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q183" s="2" t="inlineStr">
@@ -23172,17 +23168,17 @@
       </c>
       <c r="X183" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y183" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
         </is>
       </c>
       <c r="Z183" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA183" s="2" t="inlineStr">
@@ -23192,17 +23188,17 @@
       </c>
       <c r="AB183" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC183" s="2" t="inlineStr">
         <is>
-          <t>136.2</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AD183" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -23245,19 +23241,19 @@
       </c>
       <c r="I184" s="2" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>22:55</t>
         </is>
       </c>
       <c r="J184" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>121分钟</t>
         </is>
       </c>
       <c r="K184" s="2" t="inlineStr"/>
       <c r="L184" s="2" t="inlineStr"/>
       <c r="M184" s="2" t="inlineStr">
         <is>
-          <t>21:20采样：该车到重点站沪南路华夏西路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数92分钟，约±5分钟</t>
+          <t>21:50采样：该车到重点站迎春路金松路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数62分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N184" s="2" t="inlineStr">
@@ -23272,7 +23268,7 @@
       </c>
       <c r="P184" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q184" s="2" t="inlineStr">
@@ -23321,12 +23317,12 @@
       </c>
       <c r="AC184" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>131.8</t>
         </is>
       </c>
       <c r="AD184" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -24880,7 +24876,7 @@
       </c>
       <c r="P197" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="Q197" s="2" t="inlineStr">
@@ -25492,7 +25488,7 @@
       </c>
       <c r="P202" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q202" s="2" t="inlineStr">
@@ -25612,7 +25608,7 @@
       </c>
       <c r="P203" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q203" s="2" t="inlineStr">
@@ -25661,7 +25657,7 @@
       </c>
       <c r="AC203" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>79.1</t>
         </is>
       </c>
       <c r="AD203" s="2" t="inlineStr">
@@ -26844,7 +26840,7 @@
       </c>
       <c r="P213" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="Q213" s="2" t="inlineStr">
@@ -27092,7 +27088,7 @@
       </c>
       <c r="P215" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q215" s="2" t="inlineStr">
@@ -27464,7 +27460,7 @@
       </c>
       <c r="P218" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q218" s="2" t="inlineStr">
@@ -27513,7 +27509,7 @@
       </c>
       <c r="AC218" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>79.1</t>
         </is>
       </c>
       <c r="AD218" s="2" t="inlineStr">
@@ -27960,7 +27956,7 @@
       </c>
       <c r="P222" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="Q222" s="2" t="inlineStr">
@@ -28208,7 +28204,7 @@
       </c>
       <c r="P224" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q224" s="2" t="inlineStr">
@@ -28452,7 +28448,7 @@
       </c>
       <c r="P226" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q226" s="2" t="inlineStr">
@@ -28501,7 +28497,7 @@
       </c>
       <c r="AC226" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>79.1</t>
         </is>
       </c>
       <c r="AD226" s="2" t="inlineStr">
@@ -28824,7 +28820,7 @@
       </c>
       <c r="P229" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q229" s="2" t="inlineStr">
@@ -28873,7 +28869,7 @@
       </c>
       <c r="AC229" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AD229" s="2" t="inlineStr">
@@ -29812,7 +29808,7 @@
       </c>
       <c r="P237" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q237" s="2" t="inlineStr">
@@ -29861,7 +29857,7 @@
       </c>
       <c r="AC237" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AD237" s="2" t="inlineStr">
@@ -30300,7 +30296,7 @@
       </c>
       <c r="P241" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="Q241" s="2" t="inlineStr">
@@ -30548,7 +30544,7 @@
       </c>
       <c r="P243" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q243" s="2" t="inlineStr">
@@ -31292,7 +31288,7 @@
       </c>
       <c r="P249" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q249" s="2" t="inlineStr">
@@ -31341,7 +31337,7 @@
       </c>
       <c r="AC249" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>79.1</t>
         </is>
       </c>
       <c r="AD249" s="2" t="inlineStr">
@@ -31536,7 +31532,7 @@
       </c>
       <c r="P251" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q251" s="2" t="inlineStr">
@@ -31585,7 +31581,7 @@
       </c>
       <c r="AC251" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AD251" s="2" t="inlineStr">
@@ -32028,7 +32024,7 @@
       </c>
       <c r="P255" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="Q255" s="2" t="inlineStr">
@@ -32268,7 +32264,7 @@
       </c>
       <c r="P257" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q257" s="2" t="inlineStr">
@@ -33008,7 +33004,7 @@
       </c>
       <c r="P263" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q263" s="2" t="inlineStr">
@@ -33057,7 +33053,7 @@
       </c>
       <c r="AC263" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>79.1</t>
         </is>
       </c>
       <c r="AD263" s="2" t="inlineStr">
@@ -33256,7 +33252,7 @@
       </c>
       <c r="P265" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q265" s="2" t="inlineStr">
@@ -33305,7 +33301,7 @@
       </c>
       <c r="AC265" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AD265" s="2" t="inlineStr">
@@ -33876,7 +33872,7 @@
       </c>
       <c r="P270" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="Q270" s="2" t="inlineStr">
@@ -34124,7 +34120,7 @@
       </c>
       <c r="P272" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q272" s="2" t="inlineStr">
@@ -35236,7 +35232,7 @@
       </c>
       <c r="P281" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q281" s="2" t="inlineStr">
@@ -35285,7 +35281,7 @@
       </c>
       <c r="AC281" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>79.1</t>
         </is>
       </c>
       <c r="AD281" s="2" t="inlineStr">
@@ -35360,7 +35356,7 @@
       </c>
       <c r="P282" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q282" s="2" t="inlineStr">
@@ -35409,7 +35405,7 @@
       </c>
       <c r="AC282" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AD282" s="2" t="inlineStr">
@@ -35469,12 +35465,12 @@
       <c r="L283" s="2" t="inlineStr"/>
       <c r="M283" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N283" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O283" s="2" t="inlineStr">
@@ -35484,7 +35480,7 @@
       </c>
       <c r="P283" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="Q283" s="2" t="inlineStr">
@@ -35593,12 +35589,12 @@
       <c r="L284" s="2" t="inlineStr"/>
       <c r="M284" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N284" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O284" s="2" t="inlineStr">
@@ -35608,7 +35604,7 @@
       </c>
       <c r="P284" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q284" s="2" t="inlineStr">
@@ -35700,7 +35696,7 @@
       </c>
       <c r="H285" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I285" s="2" t="inlineStr">
@@ -35710,19 +35706,19 @@
       </c>
       <c r="J285" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="K285" s="2" t="inlineStr"/>
       <c r="L285" s="2" t="inlineStr"/>
       <c r="M285" s="2" t="inlineStr">
         <is>
-          <t>21:20采样：该车到重点站金杨路枣庄路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数60分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="N285" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O285" s="2" t="inlineStr">
@@ -35732,7 +35728,7 @@
       </c>
       <c r="P285" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q285" s="2" t="inlineStr">
@@ -35756,12 +35752,12 @@
       </c>
       <c r="X285" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y285" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z285" s="2" t="inlineStr">
@@ -35781,7 +35777,7 @@
       </c>
       <c r="AC285" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>79.1</t>
         </is>
       </c>
       <c r="AD285" s="2" t="inlineStr">
@@ -35829,19 +35825,19 @@
       </c>
       <c r="I286" s="2" t="inlineStr">
         <is>
-          <t>22:59</t>
+          <t>22:56</t>
         </is>
       </c>
       <c r="J286" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="K286" s="2" t="inlineStr"/>
       <c r="L286" s="2" t="inlineStr"/>
       <c r="M286" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数80分钟估算，约±5分钟</t>
+          <t>21:50采样：该车到重点站金杨路云山路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数63分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N286" s="2" t="inlineStr">
@@ -35856,7 +35852,7 @@
       </c>
       <c r="P286" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q286" s="2" t="inlineStr">
@@ -35885,7 +35881,7 @@
       </c>
       <c r="Y286" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z286" s="2" t="inlineStr">
@@ -35905,7 +35901,7 @@
       </c>
       <c r="AC286" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AD286" s="2" t="inlineStr">
